--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28122"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7C0D0ED-829C-4FFB-A578-1F86854805BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F0C72ED-C198-4D55-8763-79CAA4ABE3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="5" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="ldsurvival-baseline-cifs" sheetId="4" r:id="rId4"/>
     <sheet name="ldsurvival-baseline-vars" sheetId="5" r:id="rId5"/>
     <sheet name="ldsurvival-inputs" sheetId="6" r:id="rId6"/>
-    <sheet name="S0 estimates" sheetId="7" r:id="rId7"/>
+    <sheet name="ldsurvival-competing-mortality" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="116">
   <si>
     <t>Notes</t>
   </si>
@@ -468,16 +468,46 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Table 1</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>S0</t>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Year1</t>
+  </si>
+  <si>
+    <t>Year2</t>
+  </si>
+  <si>
+    <t>Year3</t>
+  </si>
+  <si>
+    <t>Year4</t>
+  </si>
+  <si>
+    <t>Year5</t>
+  </si>
+  <si>
+    <t>Year6</t>
+  </si>
+  <si>
+    <t>Year7</t>
+  </si>
+  <si>
+    <t>Year8</t>
+  </si>
+  <si>
+    <t>Year9</t>
+  </si>
+  <si>
+    <t>Year10</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -492,11 +522,6 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="DejaVu Sans"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -520,12 +545,6 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="DejaVu Sans"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Tahoma"/>
@@ -545,8 +564,20 @@
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,20 +614,8 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="17"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="20"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -722,213 +741,95 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="18"/>
-      </left>
-      <right style="thin">
-        <color indexed="18"/>
-      </right>
-      <top style="thin">
-        <color indexed="18"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="19"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="18"/>
-      </left>
-      <right style="thin">
-        <color indexed="19"/>
-      </right>
-      <top style="thin">
-        <color indexed="19"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="19"/>
-      </left>
-      <right style="thin">
-        <color indexed="18"/>
-      </right>
-      <top style="thin">
-        <color indexed="19"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="18"/>
-      </left>
-      <right style="thin">
-        <color indexed="18"/>
-      </right>
-      <top style="thin">
-        <color indexed="19"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="18"/>
-      </left>
-      <right style="thin">
-        <color indexed="19"/>
-      </right>
-      <top style="thin">
-        <color indexed="18"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="19"/>
-      </left>
-      <right style="thin">
-        <color indexed="18"/>
-      </right>
-      <top style="thin">
-        <color indexed="18"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="18"/>
-      </left>
-      <right style="thin">
-        <color indexed="18"/>
-      </right>
-      <top style="thin">
-        <color indexed="18"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4307,10 +4208,10 @@
       <c r="F2" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="45" t="s">
         <v>49</v>
       </c>
       <c r="I2" s="43">
@@ -4341,7 +4242,7 @@
         <v>1.2430000000000001</v>
       </c>
       <c r="F3" s="4"/>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="46" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="25">
@@ -4372,7 +4273,7 @@
         <v>1.6479999999999999</v>
       </c>
       <c r="F4" s="4"/>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="46" t="s">
         <v>55</v>
       </c>
       <c r="I4" s="25">
@@ -4403,7 +4304,7 @@
         <v>1.6479999999999999</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="58" t="s">
+      <c r="G5" s="46" t="s">
         <v>58</v>
       </c>
       <c r="I5" s="25">
@@ -4434,7 +4335,7 @@
         <v>1.8959999999999999</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="46" t="s">
         <v>61</v>
       </c>
       <c r="I6" s="25">
@@ -4465,7 +4366,7 @@
         <v>2.0139999999999998</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="46" t="s">
         <v>64</v>
       </c>
       <c r="I7" s="25">
@@ -4496,7 +4397,7 @@
         <v>2.0139999999999998</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="46" t="s">
         <v>67</v>
       </c>
       <c r="I8" s="25">
@@ -4530,7 +4431,7 @@
       <c r="G9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="58"/>
+      <c r="H9" s="46"/>
       <c r="I9" s="25">
         <v>50</v>
       </c>
@@ -4552,7 +4453,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="58"/>
+      <c r="H10" s="46"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -4582,7 +4483,7 @@
       <c r="G11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="47" t="s">
         <v>75</v>
       </c>
       <c r="I11" s="25">
@@ -4618,7 +4519,7 @@
       <c r="G12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="58"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="25">
         <v>60</v>
       </c>
@@ -4652,7 +4553,7 @@
       <c r="G13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="58"/>
+      <c r="H13" s="46"/>
       <c r="I13" s="25">
         <v>60</v>
       </c>
@@ -4674,7 +4575,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="58"/>
+      <c r="H14" s="46"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -4702,7 +4603,7 @@
         <v>47</v>
       </c>
       <c r="G15" s="4"/>
-      <c r="H15" s="60" t="s">
+      <c r="H15" s="48" t="s">
         <v>85</v>
       </c>
       <c r="I15" s="25">
@@ -4736,7 +4637,7 @@
         <v>47</v>
       </c>
       <c r="G16" s="4"/>
-      <c r="H16" s="58"/>
+      <c r="H16" s="46"/>
       <c r="I16" s="25">
         <v>70</v>
       </c>
@@ -4758,7 +4659,7 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="58"/>
+      <c r="H17" s="46"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -4786,7 +4687,7 @@
         <v>47</v>
       </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="61" t="s">
+      <c r="H18" s="49" t="s">
         <v>92</v>
       </c>
       <c r="I18" s="25">
@@ -4820,7 +4721,7 @@
         <v>47</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="58"/>
+      <c r="H19" s="46"/>
       <c r="I19" s="25">
         <v>80</v>
       </c>
@@ -4852,7 +4753,7 @@
         <v>47</v>
       </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="58"/>
+      <c r="H20" s="46"/>
       <c r="I20" s="25">
         <v>80</v>
       </c>
@@ -4884,7 +4785,7 @@
         <v>47</v>
       </c>
       <c r="G21" s="4"/>
-      <c r="H21" s="58"/>
+      <c r="H21" s="46"/>
       <c r="I21" s="25">
         <v>80</v>
       </c>
@@ -4906,7 +4807,7 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="58"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -4934,7 +4835,7 @@
         <v>47</v>
       </c>
       <c r="G23" s="4"/>
-      <c r="H23" s="61" t="s">
+      <c r="H23" s="49" t="s">
         <v>99</v>
       </c>
       <c r="I23" s="25">
@@ -4968,7 +4869,7 @@
         <v>47</v>
       </c>
       <c r="G24" s="4"/>
-      <c r="H24" s="58"/>
+      <c r="H24" s="46"/>
       <c r="I24" s="25">
         <v>90</v>
       </c>
@@ -4992,163 +4893,4685 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="14.1" customHeight="1"/>
-  <cols>
-    <col min="1" max="7" width="16.33203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="16.33203125" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9199C994-664A-440E-BB8D-640CE3FD5457}">
+  <dimension ref="A1:L123"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" customHeight="1">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:12" ht="15.75">
+      <c r="A1" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-    </row>
-    <row r="2" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C1" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="D1" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A3" s="47">
-        <v>0</v>
-      </c>
-      <c r="B3" s="48">
-        <f>$A3*12</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="49">
-        <v>1</v>
-      </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.350000000000001" customHeight="1">
+      <c r="E1" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="51">
+        <v>25</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="51">
+        <v>0</v>
+      </c>
+      <c r="D2" s="51">
+        <v>0</v>
+      </c>
+      <c r="E2" s="51">
+        <v>0</v>
+      </c>
+      <c r="F2" s="51">
+        <v>0</v>
+      </c>
+      <c r="G2" s="51">
+        <v>0</v>
+      </c>
+      <c r="H2" s="51">
+        <v>0</v>
+      </c>
+      <c r="I2" s="51">
+        <v>0</v>
+      </c>
+      <c r="J2" s="51">
+        <v>0</v>
+      </c>
+      <c r="K2" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L2" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="51">
+        <v>26</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="51">
+        <v>0</v>
+      </c>
+      <c r="D3" s="51">
+        <v>0</v>
+      </c>
+      <c r="E3" s="51">
+        <v>0</v>
+      </c>
+      <c r="F3" s="51">
+        <v>0</v>
+      </c>
+      <c r="G3" s="51">
+        <v>0</v>
+      </c>
+      <c r="H3" s="51">
+        <v>0</v>
+      </c>
+      <c r="I3" s="51">
+        <v>0</v>
+      </c>
+      <c r="J3" s="51">
+        <v>0</v>
+      </c>
+      <c r="K3" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L3" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="51">
-        <v>1</v>
-      </c>
-      <c r="B4" s="52">
-        <f>$A4*12</f>
-        <v>12</v>
-      </c>
-      <c r="C4" s="53">
-        <v>0.98499999999999999</v>
-      </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.350000000000001" customHeight="1">
+        <v>27</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="51">
+        <v>0</v>
+      </c>
+      <c r="D4" s="51">
+        <v>0</v>
+      </c>
+      <c r="E4" s="51">
+        <v>0</v>
+      </c>
+      <c r="F4" s="51">
+        <v>0</v>
+      </c>
+      <c r="G4" s="51">
+        <v>0</v>
+      </c>
+      <c r="H4" s="51">
+        <v>0</v>
+      </c>
+      <c r="I4" s="51">
+        <v>0</v>
+      </c>
+      <c r="J4" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L4" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="51">
-        <v>3</v>
-      </c>
-      <c r="B5" s="52">
-        <f>$A5*12</f>
+        <v>28</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="51">
+        <v>0</v>
+      </c>
+      <c r="D5" s="51">
+        <v>0</v>
+      </c>
+      <c r="E5" s="51">
+        <v>0</v>
+      </c>
+      <c r="F5" s="51">
+        <v>0</v>
+      </c>
+      <c r="G5" s="51">
+        <v>0</v>
+      </c>
+      <c r="H5" s="51">
+        <v>0</v>
+      </c>
+      <c r="I5" s="51">
+        <v>0</v>
+      </c>
+      <c r="J5" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L5" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="51">
+        <v>29</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="51">
+        <v>0</v>
+      </c>
+      <c r="D6" s="51">
+        <v>0</v>
+      </c>
+      <c r="E6" s="51">
+        <v>0</v>
+      </c>
+      <c r="F6" s="51">
+        <v>0</v>
+      </c>
+      <c r="G6" s="51">
+        <v>0</v>
+      </c>
+      <c r="H6" s="51">
+        <v>0</v>
+      </c>
+      <c r="I6" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J6" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L6" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="51">
+        <v>30</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="51">
+        <v>0</v>
+      </c>
+      <c r="D7" s="51">
+        <v>0</v>
+      </c>
+      <c r="E7" s="51">
+        <v>0</v>
+      </c>
+      <c r="F7" s="51">
+        <v>0</v>
+      </c>
+      <c r="G7" s="51">
+        <v>0</v>
+      </c>
+      <c r="H7" s="51">
+        <v>0</v>
+      </c>
+      <c r="I7" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J7" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L7" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="51">
+        <v>31</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="51">
+        <v>0</v>
+      </c>
+      <c r="D8" s="51">
+        <v>0</v>
+      </c>
+      <c r="E8" s="51">
+        <v>0</v>
+      </c>
+      <c r="F8" s="51">
+        <v>0</v>
+      </c>
+      <c r="G8" s="51">
+        <v>0</v>
+      </c>
+      <c r="H8" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I8" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J8" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L8" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="51">
+        <v>32</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="51">
+        <v>0</v>
+      </c>
+      <c r="D9" s="51">
+        <v>0</v>
+      </c>
+      <c r="E9" s="51">
+        <v>0</v>
+      </c>
+      <c r="F9" s="51">
+        <v>0</v>
+      </c>
+      <c r="G9" s="51">
+        <v>0</v>
+      </c>
+      <c r="H9" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I9" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J9" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L9" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="51">
+        <v>33</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="51">
+        <v>0</v>
+      </c>
+      <c r="D10" s="51">
+        <v>0</v>
+      </c>
+      <c r="E10" s="51">
+        <v>0</v>
+      </c>
+      <c r="F10" s="51">
+        <v>0</v>
+      </c>
+      <c r="G10" s="51">
+        <v>0</v>
+      </c>
+      <c r="H10" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J10" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L10" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="51">
+        <v>34</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="51">
+        <v>0</v>
+      </c>
+      <c r="D11" s="51">
+        <v>0</v>
+      </c>
+      <c r="E11" s="51">
+        <v>0</v>
+      </c>
+      <c r="F11" s="51">
+        <v>0</v>
+      </c>
+      <c r="G11" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H11" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J11" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L11" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="51">
+        <v>35</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="51">
+        <v>0</v>
+      </c>
+      <c r="D12" s="51">
+        <v>0</v>
+      </c>
+      <c r="E12" s="51">
+        <v>0</v>
+      </c>
+      <c r="F12" s="51">
+        <v>0</v>
+      </c>
+      <c r="G12" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H12" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I12" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J12" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L12" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="51">
         <v>36</v>
       </c>
-      <c r="C5" s="53">
-        <v>0.97</v>
-      </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A6" s="51">
-        <v>5</v>
-      </c>
-      <c r="B6" s="52">
-        <f>$A6*12</f>
+      <c r="B13" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="51">
+        <v>0</v>
+      </c>
+      <c r="D13" s="51">
+        <v>0</v>
+      </c>
+      <c r="E13" s="51">
+        <v>0</v>
+      </c>
+      <c r="F13" s="51">
+        <v>0</v>
+      </c>
+      <c r="G13" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H13" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J13" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L13" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="51">
+        <v>37</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="51">
+        <v>0</v>
+      </c>
+      <c r="D14" s="51">
+        <v>0</v>
+      </c>
+      <c r="E14" s="51">
+        <v>0</v>
+      </c>
+      <c r="F14" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G14" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H14" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I14" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J14" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K14" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L14" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="51">
+        <v>38</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="51">
+        <v>0</v>
+      </c>
+      <c r="D15" s="51">
+        <v>0</v>
+      </c>
+      <c r="E15" s="51">
+        <v>0</v>
+      </c>
+      <c r="F15" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H15" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J15" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K15" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L15" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="51">
+        <v>39</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="51">
+        <v>0</v>
+      </c>
+      <c r="D16" s="51">
+        <v>0</v>
+      </c>
+      <c r="E16" s="51">
+        <v>0</v>
+      </c>
+      <c r="F16" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I16" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J16" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K16" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L16" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="51">
+        <v>40</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="51">
+        <v>0</v>
+      </c>
+      <c r="D17" s="51">
+        <v>0</v>
+      </c>
+      <c r="E17" s="51">
+        <v>0</v>
+      </c>
+      <c r="F17" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H17" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J17" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K17" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L17" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="51">
+        <v>41</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="51">
+        <v>0</v>
+      </c>
+      <c r="D18" s="51">
+        <v>0</v>
+      </c>
+      <c r="E18" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F18" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I18" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J18" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K18" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L18" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="51">
+        <v>42</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="51">
+        <v>0</v>
+      </c>
+      <c r="D19" s="51">
+        <v>0</v>
+      </c>
+      <c r="E19" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F19" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G19" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H19" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I19" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J19" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K19" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L19" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="51">
+        <v>43</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="51">
+        <v>0</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0</v>
+      </c>
+      <c r="E20" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F20" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H20" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J20" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K20" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L20" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="51">
+        <v>44</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="51">
+        <v>0</v>
+      </c>
+      <c r="D21" s="51">
+        <v>0</v>
+      </c>
+      <c r="E21" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F21" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H21" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I21" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J21" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K21" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L21" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="51">
+        <v>45</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="51">
+        <v>0</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F22" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G22" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K22" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L22" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="51">
+        <v>46</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="51">
+        <v>0</v>
+      </c>
+      <c r="D23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H23" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I23" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J23" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K23" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L23" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="51">
+        <v>47</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="51">
+        <v>0</v>
+      </c>
+      <c r="D24" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E24" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F24" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G24" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H24" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I24" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J24" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K24" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L24" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="51">
+        <v>48</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="51">
+        <v>0</v>
+      </c>
+      <c r="D25" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E25" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F25" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G25" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H25" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I25" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J25" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K25" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L25" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="51">
+        <v>49</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="51">
+        <v>0</v>
+      </c>
+      <c r="D26" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F26" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G26" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H26" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I26" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J26" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K26" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L26" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="51">
+        <v>50</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="51">
+        <v>0</v>
+      </c>
+      <c r="D27" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E27" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F27" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G27" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H27" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I27" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J27" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K27" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="L27" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="51">
+        <v>51</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="51">
+        <v>0</v>
+      </c>
+      <c r="D28" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F28" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G28" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H28" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I28" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J28" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K28" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="L28" s="51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="51">
+        <v>52</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="51">
+        <v>0</v>
+      </c>
+      <c r="D29" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F29" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G29" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H29" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I29" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J29" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K29" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="L29" s="51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="51">
+        <v>53</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="51">
+        <v>0</v>
+      </c>
+      <c r="D30" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E30" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F30" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G30" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H30" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I30" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J30" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K30" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="L30" s="51">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="51">
+        <v>54</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="51">
+        <v>0</v>
+      </c>
+      <c r="D31" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E31" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F31" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G31" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H31" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I31" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="J31" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K31" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="L31" s="51">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="51">
+        <v>55</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="51">
+        <v>0</v>
+      </c>
+      <c r="D32" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E32" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F32" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G32" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H32" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I32" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="J32" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="K32" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="L32" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="51">
+        <v>56</v>
+      </c>
+      <c r="B33" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D33" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E33" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F33" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G33" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H33" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="I33" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="J33" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="K33" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="L33" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="51">
+        <v>57</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D34" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E34" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F34" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G34" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H34" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="I34" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="J34" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="K34" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L34" s="51">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="51">
+        <v>58</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D35" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E35" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F35" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G35" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="H35" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="I35" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="J35" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="K35" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L35" s="51">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="51">
+        <v>59</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E36" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F36" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G36" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="H36" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="I36" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="J36" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K36" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="L36" s="51">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="51">
         <v>60</v>
       </c>
-      <c r="C6" s="53">
-        <v>0.96199999999999997</v>
-      </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A7" s="51">
-        <v>7</v>
-      </c>
-      <c r="B7" s="52">
-        <f>$A7*12</f>
+      <c r="B37" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D37" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E37" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F37" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G37" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="H37" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="I37" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="J37" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="K37" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="L37" s="51">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="51">
+        <v>61</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D38" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E38" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F38" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="G38" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="H38" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="I38" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J38" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="K38" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="51">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="51">
+        <v>62</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D39" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E39" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F39" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="G39" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="H39" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="I39" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="J39" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="K39" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="L39" s="51">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="51">
+        <v>63</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E40" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F40" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="G40" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="H40" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I40" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="J40" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="K40" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="L40" s="51">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="51">
+        <v>64</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D41" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E41" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F41" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="G41" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="H41" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="I41" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="J41" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="K41" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="L41" s="51">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="51">
+        <v>65</v>
+      </c>
+      <c r="B42" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D42" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="F42" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="G42" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H42" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="I42" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="J42" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="K42" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L42" s="51">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="51">
+        <v>66</v>
+      </c>
+      <c r="B43" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D43" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E43" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="F43" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="G43" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H43" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="I43" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="J43" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="K43" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="L43" s="51">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="51">
+        <v>67</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D44" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E44" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="F44" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="G44" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="H44" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="J44" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K44" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="L44" s="51">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="51">
+        <v>68</v>
+      </c>
+      <c r="B45" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E45" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="F45" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G45" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="H45" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="I45" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="J45" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="K45" s="51">
+        <v>0.18</v>
+      </c>
+      <c r="L45" s="51">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="51">
+        <v>69</v>
+      </c>
+      <c r="B46" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D46" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E46" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="F46" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G46" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="H46" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="I46" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J46" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="K46" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="L46" s="51">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="51">
+        <v>70</v>
+      </c>
+      <c r="B47" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D47" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="E47" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="F47" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="G47" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="H47" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="I47" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="J47" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="K47" s="51">
+        <v>0.22</v>
+      </c>
+      <c r="L47" s="51">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="51">
+        <v>71</v>
+      </c>
+      <c r="B48" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D48" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="E48" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="F48" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="G48" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="H48" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I48" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="J48" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="K48" s="51">
+        <v>0.24</v>
+      </c>
+      <c r="L48" s="51">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="51">
+        <v>72</v>
+      </c>
+      <c r="B49" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D49" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E49" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F49" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="G49" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="H49" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="I49" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="J49" s="51">
+        <v>0.23</v>
+      </c>
+      <c r="K49" s="51">
+        <v>0.26</v>
+      </c>
+      <c r="L49" s="51">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="51">
+        <v>73</v>
+      </c>
+      <c r="B50" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E50" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="F50" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="G50" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H50" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="I50" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="J50" s="51">
+        <v>0.25</v>
+      </c>
+      <c r="K50" s="51">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L50" s="51">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="51">
+        <v>74</v>
+      </c>
+      <c r="B51" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="D51" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="E51" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="F51" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="G51" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="H51" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="I51" s="51">
+        <v>0.23</v>
+      </c>
+      <c r="J51" s="51">
+        <v>0.27</v>
+      </c>
+      <c r="K51" s="51">
+        <v>0.32</v>
+      </c>
+      <c r="L51" s="51">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="51">
+        <v>75</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="D52" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="E52" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="F52" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="G52" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="H52" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="I52" s="51">
+        <v>0.25</v>
+      </c>
+      <c r="J52" s="51">
+        <v>0.3</v>
+      </c>
+      <c r="K52" s="51">
+        <v>0.35</v>
+      </c>
+      <c r="L52" s="51">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="51">
+        <v>76</v>
+      </c>
+      <c r="B53" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="D53" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E53" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="F53" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="G53" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="H53" s="51">
+        <v>0.23</v>
+      </c>
+      <c r="I53" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J53" s="51">
+        <v>0.33</v>
+      </c>
+      <c r="K53" s="51">
+        <v>0.38</v>
+      </c>
+      <c r="L53" s="51">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="51">
+        <v>77</v>
+      </c>
+      <c r="B54" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="D54" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="E54" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="F54" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="G54" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="H54" s="51">
+        <v>0.26</v>
+      </c>
+      <c r="I54" s="51">
+        <v>0.31</v>
+      </c>
+      <c r="J54" s="51">
+        <v>0.36</v>
+      </c>
+      <c r="K54" s="51">
+        <v>0.42</v>
+      </c>
+      <c r="L54" s="51">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="51">
+        <v>78</v>
+      </c>
+      <c r="B55" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="D55" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="E55" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="F55" s="51">
+        <v>0.18</v>
+      </c>
+      <c r="G55" s="51">
+        <v>0.23</v>
+      </c>
+      <c r="H55" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I55" s="51">
+        <v>0.34</v>
+      </c>
+      <c r="J55" s="51">
+        <v>0.4</v>
+      </c>
+      <c r="K55" s="51">
+        <v>0.46</v>
+      </c>
+      <c r="L55" s="51">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="51">
+        <v>79</v>
+      </c>
+      <c r="B56" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="D56" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="E56" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="F56" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="G56" s="51">
+        <v>0.26</v>
+      </c>
+      <c r="H56" s="51">
+        <v>0.31</v>
+      </c>
+      <c r="I56" s="51">
+        <v>0.37</v>
+      </c>
+      <c r="J56" s="51">
+        <v>0.44</v>
+      </c>
+      <c r="K56" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="L56" s="51">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="51">
+        <v>80</v>
+      </c>
+      <c r="B57" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="D57" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="E57" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="F57" s="51">
+        <v>0.22</v>
+      </c>
+      <c r="G57" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H57" s="51">
+        <v>0.35</v>
+      </c>
+      <c r="I57" s="51">
+        <v>0.41</v>
+      </c>
+      <c r="J57" s="51">
+        <v>0.48</v>
+      </c>
+      <c r="K57" s="51">
+        <v>0.54</v>
+      </c>
+      <c r="L57" s="51">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="51">
+        <v>81</v>
+      </c>
+      <c r="B58" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="D58" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="E58" s="51">
+        <v>0.18</v>
+      </c>
+      <c r="F58" s="51">
+        <v>0.25</v>
+      </c>
+      <c r="G58" s="51">
+        <v>0.31</v>
+      </c>
+      <c r="H58" s="51">
+        <v>0.38</v>
+      </c>
+      <c r="I58" s="51">
+        <v>0.45</v>
+      </c>
+      <c r="J58" s="51">
+        <v>0.52</v>
+      </c>
+      <c r="K58" s="51">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L58" s="51">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="51">
+        <v>82</v>
+      </c>
+      <c r="B59" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D59" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="E59" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="F59" s="51">
+        <v>0.27</v>
+      </c>
+      <c r="G59" s="51">
+        <v>0.35</v>
+      </c>
+      <c r="H59" s="51">
+        <v>0.42</v>
+      </c>
+      <c r="I59" s="51">
+        <v>0.49</v>
+      </c>
+      <c r="J59" s="51">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K59" s="51">
+        <v>0.63</v>
+      </c>
+      <c r="L59" s="51">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="51">
+        <v>83</v>
+      </c>
+      <c r="B60" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D60" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="E60" s="51">
+        <v>0.23</v>
+      </c>
+      <c r="F60" s="51">
+        <v>0.3</v>
+      </c>
+      <c r="G60" s="51">
+        <v>0.38</v>
+      </c>
+      <c r="H60" s="51">
+        <v>0.46</v>
+      </c>
+      <c r="I60" s="51">
+        <v>0.53</v>
+      </c>
+      <c r="J60" s="51">
+        <v>0.6</v>
+      </c>
+      <c r="K60" s="51">
+        <v>0.67</v>
+      </c>
+      <c r="L60" s="51">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="51">
         <v>84</v>
       </c>
-      <c r="C7" s="53">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A8" s="51">
-        <v>10</v>
-      </c>
-      <c r="B8" s="52">
-        <f>$A8*12</f>
-        <v>120</v>
-      </c>
-      <c r="C8" s="53">
-        <v>0.94899999999999995</v>
-      </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A9" s="55"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A10" s="55"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A11" s="55"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
+      <c r="B61" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="D61" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="E61" s="51">
+        <v>0.25</v>
+      </c>
+      <c r="F61" s="51">
+        <v>0.34</v>
+      </c>
+      <c r="G61" s="51">
+        <v>0.42</v>
+      </c>
+      <c r="H61" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="I61" s="51">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J61" s="51">
+        <v>0.64</v>
+      </c>
+      <c r="K61" s="51">
+        <v>0.71</v>
+      </c>
+      <c r="L61" s="51">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="51">
+        <v>85</v>
+      </c>
+      <c r="B62" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="D62" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="E62" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F62" s="51">
+        <v>0.37</v>
+      </c>
+      <c r="G62" s="51">
+        <v>0.46</v>
+      </c>
+      <c r="H62" s="51">
+        <v>0.54</v>
+      </c>
+      <c r="I62" s="51">
+        <v>0.62</v>
+      </c>
+      <c r="J62" s="51">
+        <v>0.69</v>
+      </c>
+      <c r="K62" s="51">
+        <v>0.75</v>
+      </c>
+      <c r="L62" s="51">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="51">
+        <v>25</v>
+      </c>
+      <c r="B63" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" s="51">
+        <v>0</v>
+      </c>
+      <c r="D63" s="51">
+        <v>0</v>
+      </c>
+      <c r="E63" s="51">
+        <v>0</v>
+      </c>
+      <c r="F63" s="51">
+        <v>0</v>
+      </c>
+      <c r="G63" s="51">
+        <v>0</v>
+      </c>
+      <c r="H63" s="51">
+        <v>0</v>
+      </c>
+      <c r="I63" s="51">
+        <v>0</v>
+      </c>
+      <c r="J63" s="51">
+        <v>0</v>
+      </c>
+      <c r="K63" s="51">
+        <v>0</v>
+      </c>
+      <c r="L63" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="51">
+        <v>26</v>
+      </c>
+      <c r="B64" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="51">
+        <v>0</v>
+      </c>
+      <c r="D64" s="51">
+        <v>0</v>
+      </c>
+      <c r="E64" s="51">
+        <v>0</v>
+      </c>
+      <c r="F64" s="51">
+        <v>0</v>
+      </c>
+      <c r="G64" s="51">
+        <v>0</v>
+      </c>
+      <c r="H64" s="51">
+        <v>0</v>
+      </c>
+      <c r="I64" s="51">
+        <v>0</v>
+      </c>
+      <c r="J64" s="51">
+        <v>0</v>
+      </c>
+      <c r="K64" s="51">
+        <v>0</v>
+      </c>
+      <c r="L64" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="51">
+        <v>27</v>
+      </c>
+      <c r="B65" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65" s="51">
+        <v>0</v>
+      </c>
+      <c r="D65" s="51">
+        <v>0</v>
+      </c>
+      <c r="E65" s="51">
+        <v>0</v>
+      </c>
+      <c r="F65" s="51">
+        <v>0</v>
+      </c>
+      <c r="G65" s="51">
+        <v>0</v>
+      </c>
+      <c r="H65" s="51">
+        <v>0</v>
+      </c>
+      <c r="I65" s="51">
+        <v>0</v>
+      </c>
+      <c r="J65" s="51">
+        <v>0</v>
+      </c>
+      <c r="K65" s="51">
+        <v>0</v>
+      </c>
+      <c r="L65" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="51">
+        <v>28</v>
+      </c>
+      <c r="B66" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="51">
+        <v>0</v>
+      </c>
+      <c r="D66" s="51">
+        <v>0</v>
+      </c>
+      <c r="E66" s="51">
+        <v>0</v>
+      </c>
+      <c r="F66" s="51">
+        <v>0</v>
+      </c>
+      <c r="G66" s="51">
+        <v>0</v>
+      </c>
+      <c r="H66" s="51">
+        <v>0</v>
+      </c>
+      <c r="I66" s="51">
+        <v>0</v>
+      </c>
+      <c r="J66" s="51">
+        <v>0</v>
+      </c>
+      <c r="K66" s="51">
+        <v>0</v>
+      </c>
+      <c r="L66" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="51">
+        <v>29</v>
+      </c>
+      <c r="B67" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="51">
+        <v>0</v>
+      </c>
+      <c r="D67" s="51">
+        <v>0</v>
+      </c>
+      <c r="E67" s="51">
+        <v>0</v>
+      </c>
+      <c r="F67" s="51">
+        <v>0</v>
+      </c>
+      <c r="G67" s="51">
+        <v>0</v>
+      </c>
+      <c r="H67" s="51">
+        <v>0</v>
+      </c>
+      <c r="I67" s="51">
+        <v>0</v>
+      </c>
+      <c r="J67" s="51">
+        <v>0</v>
+      </c>
+      <c r="K67" s="51">
+        <v>0</v>
+      </c>
+      <c r="L67" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="51">
+        <v>30</v>
+      </c>
+      <c r="B68" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="51">
+        <v>0</v>
+      </c>
+      <c r="D68" s="51">
+        <v>0</v>
+      </c>
+      <c r="E68" s="51">
+        <v>0</v>
+      </c>
+      <c r="F68" s="51">
+        <v>0</v>
+      </c>
+      <c r="G68" s="51">
+        <v>0</v>
+      </c>
+      <c r="H68" s="51">
+        <v>0</v>
+      </c>
+      <c r="I68" s="51">
+        <v>0</v>
+      </c>
+      <c r="J68" s="51">
+        <v>0</v>
+      </c>
+      <c r="K68" s="51">
+        <v>0</v>
+      </c>
+      <c r="L68" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="51">
+        <v>31</v>
+      </c>
+      <c r="B69" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C69" s="51">
+        <v>0</v>
+      </c>
+      <c r="D69" s="51">
+        <v>0</v>
+      </c>
+      <c r="E69" s="51">
+        <v>0</v>
+      </c>
+      <c r="F69" s="51">
+        <v>0</v>
+      </c>
+      <c r="G69" s="51">
+        <v>0</v>
+      </c>
+      <c r="H69" s="51">
+        <v>0</v>
+      </c>
+      <c r="I69" s="51">
+        <v>0</v>
+      </c>
+      <c r="J69" s="51">
+        <v>0</v>
+      </c>
+      <c r="K69" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L69" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="51">
+        <v>32</v>
+      </c>
+      <c r="B70" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C70" s="51">
+        <v>0</v>
+      </c>
+      <c r="D70" s="51">
+        <v>0</v>
+      </c>
+      <c r="E70" s="51">
+        <v>0</v>
+      </c>
+      <c r="F70" s="51">
+        <v>0</v>
+      </c>
+      <c r="G70" s="51">
+        <v>0</v>
+      </c>
+      <c r="H70" s="51">
+        <v>0</v>
+      </c>
+      <c r="I70" s="51">
+        <v>0</v>
+      </c>
+      <c r="J70" s="51">
+        <v>0</v>
+      </c>
+      <c r="K70" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L70" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="51">
+        <v>33</v>
+      </c>
+      <c r="B71" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C71" s="51">
+        <v>0</v>
+      </c>
+      <c r="D71" s="51">
+        <v>0</v>
+      </c>
+      <c r="E71" s="51">
+        <v>0</v>
+      </c>
+      <c r="F71" s="51">
+        <v>0</v>
+      </c>
+      <c r="G71" s="51">
+        <v>0</v>
+      </c>
+      <c r="H71" s="51">
+        <v>0</v>
+      </c>
+      <c r="I71" s="51">
+        <v>0</v>
+      </c>
+      <c r="J71" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K71" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L71" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="51">
+        <v>34</v>
+      </c>
+      <c r="B72" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C72" s="51">
+        <v>0</v>
+      </c>
+      <c r="D72" s="51">
+        <v>0</v>
+      </c>
+      <c r="E72" s="51">
+        <v>0</v>
+      </c>
+      <c r="F72" s="51">
+        <v>0</v>
+      </c>
+      <c r="G72" s="51">
+        <v>0</v>
+      </c>
+      <c r="H72" s="51">
+        <v>0</v>
+      </c>
+      <c r="I72" s="51">
+        <v>0</v>
+      </c>
+      <c r="J72" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K72" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L72" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="51">
+        <v>35</v>
+      </c>
+      <c r="B73" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="51">
+        <v>0</v>
+      </c>
+      <c r="D73" s="51">
+        <v>0</v>
+      </c>
+      <c r="E73" s="51">
+        <v>0</v>
+      </c>
+      <c r="F73" s="51">
+        <v>0</v>
+      </c>
+      <c r="G73" s="51">
+        <v>0</v>
+      </c>
+      <c r="H73" s="51">
+        <v>0</v>
+      </c>
+      <c r="I73" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J73" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K73" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L73" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="51">
+        <v>36</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="51">
+        <v>0</v>
+      </c>
+      <c r="D74" s="51">
+        <v>0</v>
+      </c>
+      <c r="E74" s="51">
+        <v>0</v>
+      </c>
+      <c r="F74" s="51">
+        <v>0</v>
+      </c>
+      <c r="G74" s="51">
+        <v>0</v>
+      </c>
+      <c r="H74" s="51">
+        <v>0</v>
+      </c>
+      <c r="I74" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J74" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K74" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L74" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="51">
+        <v>37</v>
+      </c>
+      <c r="B75" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C75" s="51">
+        <v>0</v>
+      </c>
+      <c r="D75" s="51">
+        <v>0</v>
+      </c>
+      <c r="E75" s="51">
+        <v>0</v>
+      </c>
+      <c r="F75" s="51">
+        <v>0</v>
+      </c>
+      <c r="G75" s="51">
+        <v>0</v>
+      </c>
+      <c r="H75" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I75" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J75" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K75" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L75" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="51">
+        <v>38</v>
+      </c>
+      <c r="B76" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" s="51">
+        <v>0</v>
+      </c>
+      <c r="D76" s="51">
+        <v>0</v>
+      </c>
+      <c r="E76" s="51">
+        <v>0</v>
+      </c>
+      <c r="F76" s="51">
+        <v>0</v>
+      </c>
+      <c r="G76" s="51">
+        <v>0</v>
+      </c>
+      <c r="H76" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I76" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J76" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K76" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L76" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="51">
+        <v>39</v>
+      </c>
+      <c r="B77" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="51">
+        <v>0</v>
+      </c>
+      <c r="D77" s="51">
+        <v>0</v>
+      </c>
+      <c r="E77" s="51">
+        <v>0</v>
+      </c>
+      <c r="F77" s="51">
+        <v>0</v>
+      </c>
+      <c r="G77" s="51">
+        <v>0</v>
+      </c>
+      <c r="H77" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I77" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J77" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K77" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L77" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="51">
+        <v>40</v>
+      </c>
+      <c r="B78" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C78" s="51">
+        <v>0</v>
+      </c>
+      <c r="D78" s="51">
+        <v>0</v>
+      </c>
+      <c r="E78" s="51">
+        <v>0</v>
+      </c>
+      <c r="F78" s="51">
+        <v>0</v>
+      </c>
+      <c r="G78" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H78" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I78" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J78" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K78" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L78" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="51">
+        <v>41</v>
+      </c>
+      <c r="B79" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C79" s="51">
+        <v>0</v>
+      </c>
+      <c r="D79" s="51">
+        <v>0</v>
+      </c>
+      <c r="E79" s="51">
+        <v>0</v>
+      </c>
+      <c r="F79" s="51">
+        <v>0</v>
+      </c>
+      <c r="G79" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H79" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I79" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J79" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K79" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L79" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="51">
+        <v>42</v>
+      </c>
+      <c r="B80" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C80" s="51">
+        <v>0</v>
+      </c>
+      <c r="D80" s="51">
+        <v>0</v>
+      </c>
+      <c r="E80" s="51">
+        <v>0</v>
+      </c>
+      <c r="F80" s="51">
+        <v>0</v>
+      </c>
+      <c r="G80" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H80" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I80" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J80" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K80" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L80" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="51">
+        <v>43</v>
+      </c>
+      <c r="B81" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C81" s="51">
+        <v>0</v>
+      </c>
+      <c r="D81" s="51">
+        <v>0</v>
+      </c>
+      <c r="E81" s="51">
+        <v>0</v>
+      </c>
+      <c r="F81" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G81" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H81" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I81" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J81" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K81" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L81" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="51">
+        <v>44</v>
+      </c>
+      <c r="B82" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C82" s="51">
+        <v>0</v>
+      </c>
+      <c r="D82" s="51">
+        <v>0</v>
+      </c>
+      <c r="E82" s="51">
+        <v>0</v>
+      </c>
+      <c r="F82" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G82" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H82" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I82" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J82" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K82" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L82" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="51">
+        <v>45</v>
+      </c>
+      <c r="B83" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="51">
+        <v>0</v>
+      </c>
+      <c r="D83" s="51">
+        <v>0</v>
+      </c>
+      <c r="E83" s="51">
+        <v>0</v>
+      </c>
+      <c r="F83" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G83" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H83" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I83" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J83" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K83" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L83" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="51">
+        <v>46</v>
+      </c>
+      <c r="B84" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C84" s="51">
+        <v>0</v>
+      </c>
+      <c r="D84" s="51">
+        <v>0</v>
+      </c>
+      <c r="E84" s="51">
+        <v>0</v>
+      </c>
+      <c r="F84" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G84" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H84" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I84" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J84" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K84" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L84" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="51">
+        <v>47</v>
+      </c>
+      <c r="B85" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85" s="51">
+        <v>0</v>
+      </c>
+      <c r="D85" s="51">
+        <v>0</v>
+      </c>
+      <c r="E85" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F85" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G85" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H85" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I85" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J85" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K85" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L85" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="51">
+        <v>48</v>
+      </c>
+      <c r="B86" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C86" s="51">
+        <v>0</v>
+      </c>
+      <c r="D86" s="51">
+        <v>0</v>
+      </c>
+      <c r="E86" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F86" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G86" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H86" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I86" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J86" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K86" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L86" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="51">
+        <v>49</v>
+      </c>
+      <c r="B87" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C87" s="51">
+        <v>0</v>
+      </c>
+      <c r="D87" s="51">
+        <v>0</v>
+      </c>
+      <c r="E87" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F87" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G87" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H87" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I87" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J87" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K87" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L87" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="51">
+        <v>50</v>
+      </c>
+      <c r="B88" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C88" s="51">
+        <v>0</v>
+      </c>
+      <c r="D88" s="51">
+        <v>0</v>
+      </c>
+      <c r="E88" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F88" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G88" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H88" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="I88" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J88" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K88" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L88" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="51">
+        <v>51</v>
+      </c>
+      <c r="B89" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" s="51">
+        <v>0</v>
+      </c>
+      <c r="D89" s="51">
+        <v>0</v>
+      </c>
+      <c r="E89" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F89" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G89" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H89" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I89" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J89" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K89" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L89" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="51">
+        <v>52</v>
+      </c>
+      <c r="B90" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C90" s="51">
+        <v>0</v>
+      </c>
+      <c r="D90" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E90" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F90" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G90" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="H90" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I90" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J90" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K90" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L90" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="51">
+        <v>53</v>
+      </c>
+      <c r="B91" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C91" s="51">
+        <v>0</v>
+      </c>
+      <c r="D91" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E91" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F91" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G91" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H91" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I91" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J91" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K91" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L91" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="51">
+        <v>54</v>
+      </c>
+      <c r="B92" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C92" s="51">
+        <v>0</v>
+      </c>
+      <c r="D92" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E92" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F92" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G92" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H92" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I92" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J92" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K92" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="L92" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="51">
+        <v>55</v>
+      </c>
+      <c r="B93" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C93" s="51">
+        <v>0</v>
+      </c>
+      <c r="D93" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E93" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F93" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="G93" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H93" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I93" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J93" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K93" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="L93" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="51">
+        <v>56</v>
+      </c>
+      <c r="B94" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C94" s="51">
+        <v>0</v>
+      </c>
+      <c r="D94" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E94" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F94" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G94" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H94" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="I94" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J94" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K94" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="L94" s="51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="51">
+        <v>57</v>
+      </c>
+      <c r="B95" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" s="51">
+        <v>0</v>
+      </c>
+      <c r="D95" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E95" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F95" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G95" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H95" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I95" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J95" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K95" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="L95" s="51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" s="51">
+        <v>58</v>
+      </c>
+      <c r="B96" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C96" s="51">
+        <v>0</v>
+      </c>
+      <c r="D96" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E96" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F96" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G96" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="H96" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I96" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="J96" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K96" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="L96" s="51">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="51">
+        <v>59</v>
+      </c>
+      <c r="B97" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="51">
+        <v>0</v>
+      </c>
+      <c r="D97" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E97" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="F97" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G97" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H97" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="I97" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="J97" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="K97" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="L97" s="51">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="51">
+        <v>60</v>
+      </c>
+      <c r="B98" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C98" s="51">
+        <v>0</v>
+      </c>
+      <c r="D98" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E98" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F98" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G98" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H98" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="I98" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="J98" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="K98" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="L98" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="51">
+        <v>61</v>
+      </c>
+      <c r="B99" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C99" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D99" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E99" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F99" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="G99" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H99" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="I99" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="J99" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="K99" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L99" s="51">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="51">
+        <v>62</v>
+      </c>
+      <c r="B100" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C100" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D100" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E100" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F100" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G100" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="H100" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="I100" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="J100" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="K100" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L100" s="51">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="51">
+        <v>63</v>
+      </c>
+      <c r="B101" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C101" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D101" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E101" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F101" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G101" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="H101" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="I101" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="J101" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K101" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="L101" s="51">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="51">
+        <v>64</v>
+      </c>
+      <c r="B102" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C102" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D102" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E102" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F102" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G102" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="H102" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="I102" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="J102" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K102" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="L102" s="51">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="51">
+        <v>65</v>
+      </c>
+      <c r="B103" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C103" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D103" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E103" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="F103" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="G103" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="H103" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="I103" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J103" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="K103" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="L103" s="51">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" s="51">
+        <v>66</v>
+      </c>
+      <c r="B104" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D104" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E104" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F104" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="G104" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="H104" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="I104" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J104" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="K104" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="L104" s="51">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" s="51">
+        <v>67</v>
+      </c>
+      <c r="B105" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D105" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E105" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F105" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="G105" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="H105" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I105" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="J105" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="K105" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="L105" s="51">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" s="51">
+        <v>68</v>
+      </c>
+      <c r="B106" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C106" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D106" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E106" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="F106" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="G106" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="H106" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I106" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="J106" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="K106" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="L106" s="51">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" s="51">
+        <v>69</v>
+      </c>
+      <c r="B107" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C107" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D107" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E107" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="F107" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="G107" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="H107" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="I107" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="J107" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="K107" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L107" s="51">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" s="51">
+        <v>70</v>
+      </c>
+      <c r="B108" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C108" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D108" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E108" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="F108" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="G108" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H108" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="I108" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="J108" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="K108" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="L108" s="51">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" s="51">
+        <v>71</v>
+      </c>
+      <c r="B109" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C109" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D109" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E109" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="F109" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="G109" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="H109" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="I109" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="J109" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="K109" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="L109" s="51">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" s="51">
+        <v>72</v>
+      </c>
+      <c r="B110" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C110" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="D110" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E110" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="F110" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G110" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="H110" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="I110" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J110" s="51">
+        <v>0.16</v>
+      </c>
+      <c r="K110" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="L110" s="51">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" s="51">
+        <v>73</v>
+      </c>
+      <c r="B111" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C111" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D111" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="E111" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="F111" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="G111" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="H111" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="I111" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="J111" s="51">
+        <v>0.18</v>
+      </c>
+      <c r="K111" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="L111" s="51">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" s="51">
+        <v>74</v>
+      </c>
+      <c r="B112" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C112" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D112" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="E112" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="F112" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="G112" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="H112" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I112" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="J112" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="K112" s="51">
+        <v>0.24</v>
+      </c>
+      <c r="L112" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" s="51">
+        <v>75</v>
+      </c>
+      <c r="B113" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C113" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D113" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="E113" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F113" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="G113" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="H113" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="I113" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="J113" s="51">
+        <v>0.22</v>
+      </c>
+      <c r="K113" s="51">
+        <v>0.26</v>
+      </c>
+      <c r="L113" s="51">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" s="51">
+        <v>76</v>
+      </c>
+      <c r="B114" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C114" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="D114" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E114" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="F114" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="G114" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H114" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="I114" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="J114" s="51">
+        <v>0.25</v>
+      </c>
+      <c r="K114" s="51">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L114" s="51">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" s="51">
+        <v>77</v>
+      </c>
+      <c r="B115" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C115" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="D115" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E115" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="F115" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="G115" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="H115" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="I115" s="51">
+        <v>0.23</v>
+      </c>
+      <c r="J115" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K115" s="51">
+        <v>0.33</v>
+      </c>
+      <c r="L115" s="51">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" s="51">
+        <v>78</v>
+      </c>
+      <c r="B116" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C116" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="D116" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="E116" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="F116" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="G116" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="H116" s="51">
+        <v>0.22</v>
+      </c>
+      <c r="I116" s="51">
+        <v>0.26</v>
+      </c>
+      <c r="J116" s="51">
+        <v>0.31</v>
+      </c>
+      <c r="K116" s="51">
+        <v>0.36</v>
+      </c>
+      <c r="L116" s="51">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" s="51">
+        <v>79</v>
+      </c>
+      <c r="B117" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C117" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="D117" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E117" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="F117" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="G117" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="H117" s="51">
+        <v>0.24</v>
+      </c>
+      <c r="I117" s="51">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J117" s="51">
+        <v>0.35</v>
+      </c>
+      <c r="K117" s="51">
+        <v>0.4</v>
+      </c>
+      <c r="L117" s="51">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" s="51">
+        <v>80</v>
+      </c>
+      <c r="B118" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C118" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="D118" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="E118" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="F118" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="G118" s="51">
+        <v>0.22</v>
+      </c>
+      <c r="H118" s="51">
+        <v>0.27</v>
+      </c>
+      <c r="I118" s="51">
+        <v>0.33</v>
+      </c>
+      <c r="J118" s="51">
+        <v>0.39</v>
+      </c>
+      <c r="K118" s="51">
+        <v>0.45</v>
+      </c>
+      <c r="L118" s="51">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" s="51">
+        <v>81</v>
+      </c>
+      <c r="B119" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C119" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="D119" s="51">
+        <v>0.09</v>
+      </c>
+      <c r="E119" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F119" s="51">
+        <v>0.19</v>
+      </c>
+      <c r="G119" s="51">
+        <v>0.25</v>
+      </c>
+      <c r="H119" s="51">
+        <v>0.3</v>
+      </c>
+      <c r="I119" s="51">
+        <v>0.36</v>
+      </c>
+      <c r="J119" s="51">
+        <v>0.43</v>
+      </c>
+      <c r="K119" s="51">
+        <v>0.49</v>
+      </c>
+      <c r="L119" s="51">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" s="51">
+        <v>82</v>
+      </c>
+      <c r="B120" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C120" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="D120" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="E120" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="F120" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="G120" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H120" s="51">
+        <v>0.34</v>
+      </c>
+      <c r="I120" s="51">
+        <v>0.4</v>
+      </c>
+      <c r="J120" s="51">
+        <v>0.47</v>
+      </c>
+      <c r="K120" s="51">
+        <v>0.54</v>
+      </c>
+      <c r="L120" s="51">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" s="51">
+        <v>83</v>
+      </c>
+      <c r="B121" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C121" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="D121" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="E121" s="51">
+        <v>0.18</v>
+      </c>
+      <c r="F121" s="51">
+        <v>0.24</v>
+      </c>
+      <c r="G121" s="51">
+        <v>0.31</v>
+      </c>
+      <c r="H121" s="51">
+        <v>0.38</v>
+      </c>
+      <c r="I121" s="51">
+        <v>0.45</v>
+      </c>
+      <c r="J121" s="51">
+        <v>0.52</v>
+      </c>
+      <c r="K121" s="51">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L121" s="51">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" s="51">
+        <v>84</v>
+      </c>
+      <c r="B122" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C122" s="51">
+        <v>0.06</v>
+      </c>
+      <c r="D122" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="E122" s="51">
+        <v>0.2</v>
+      </c>
+      <c r="F122" s="51">
+        <v>0.27</v>
+      </c>
+      <c r="G122" s="51">
+        <v>0.34</v>
+      </c>
+      <c r="H122" s="51">
+        <v>0.42</v>
+      </c>
+      <c r="I122" s="51">
+        <v>0.49</v>
+      </c>
+      <c r="J122" s="51">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K122" s="51">
+        <v>0.63</v>
+      </c>
+      <c r="L122" s="51">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" s="51">
+        <v>85</v>
+      </c>
+      <c r="B123" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C123" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D123" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="E123" s="51">
+        <v>0.22</v>
+      </c>
+      <c r="F123" s="51">
+        <v>0.3</v>
+      </c>
+      <c r="G123" s="51">
+        <v>0.38</v>
+      </c>
+      <c r="H123" s="51">
+        <v>0.46</v>
+      </c>
+      <c r="I123" s="51">
+        <v>0.53</v>
+      </c>
+      <c r="J123" s="51">
+        <v>0.61</v>
+      </c>
+      <c r="K123" s="51">
+        <v>0.68</v>
+      </c>
+      <c r="L123" s="51">
+        <v>0.74</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup orientation="portrait"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28207"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F0C72ED-C198-4D55-8763-79CAA4ABE3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{180707A5-4DC6-4B3B-BE1A-926D279642D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="5" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="125">
   <si>
     <t>Notes</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>:histologic-tumor-necrosis</t>
+  </si>
+  <si>
+    <t>:age-at-surgery</t>
+  </si>
+  <si>
+    <t>:sex</t>
   </si>
   <si>
     <t>:factor-name</t>
@@ -468,10 +474,31 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Age at surgery</t>
+  </si>
+  <si>
+    <t>{:dps 0, :max 85, :min 25, :type :numeric}</t>
+  </si>
+  <si>
+    <t>[:p "Age when the kidney cancer surgery was performed. An age between 25 and 85 may be entered here."]</t>
+  </si>
+  <si>
+    <t>:Male</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>:Female</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
     <t>Age</t>
-  </si>
-  <si>
-    <t>Sex</t>
   </si>
   <si>
     <t>Year1</t>
@@ -745,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -830,6 +857,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4089,16 +4118,24 @@
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="33" t="s">
+        <v>33</v>
+      </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="16"/>
+      <c r="C7" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="4"/>
+      <c r="A8" s="33" t="s">
+        <v>34</v>
+      </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="16"/>
+      <c r="C8" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
     </row>
@@ -4127,10 +4164,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
@@ -4153,40 +4190,40 @@
         <v>25</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J1" s="39" t="s">
         <v>26</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M1" s="40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="156.94999999999999" customHeight="1">
@@ -4194,25 +4231,25 @@
         <v>30</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="43">
+        <v>48</v>
+      </c>
+      <c r="E2" s="52">
         <v>0</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I2" s="43">
         <v>50</v>
@@ -4220,7 +4257,7 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
       <c r="L2" s="42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M2" s="23"/>
       <c r="N2" s="44">
@@ -4232,18 +4269,18 @@
         <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="25">
+        <v>53</v>
+      </c>
+      <c r="E3" s="53">
         <v>1.2430000000000001</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I3" s="25">
         <v>50</v>
@@ -4251,7 +4288,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="44">
@@ -4263,18 +4300,18 @@
         <v>30</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="25">
+        <v>56</v>
+      </c>
+      <c r="E4" s="53">
         <v>1.6479999999999999</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I4" s="25">
         <v>50</v>
@@ -4282,7 +4319,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="44">
@@ -4294,18 +4331,18 @@
         <v>30</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="25">
+        <v>59</v>
+      </c>
+      <c r="E5" s="53">
         <v>1.6479999999999999</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="46" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I5" s="25">
         <v>50</v>
@@ -4313,7 +4350,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="44">
@@ -4325,18 +4362,18 @@
         <v>30</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="25">
+        <v>62</v>
+      </c>
+      <c r="E6" s="53">
         <v>1.8959999999999999</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I6" s="25">
         <v>50</v>
@@ -4344,7 +4381,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="44">
@@ -4356,18 +4393,18 @@
         <v>30</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="25">
+        <v>65</v>
+      </c>
+      <c r="E7" s="53">
         <v>2.0139999999999998</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="46" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I7" s="25">
         <v>50</v>
@@ -4375,7 +4412,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="44">
@@ -4387,18 +4424,18 @@
         <v>30</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="25">
+        <v>68</v>
+      </c>
+      <c r="E8" s="53">
         <v>2.0139999999999998</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="46" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I8" s="25">
         <v>50</v>
@@ -4406,7 +4443,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="44">
@@ -4418,18 +4455,18 @@
         <v>30</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="25">
+        <v>71</v>
+      </c>
+      <c r="E9" s="53">
         <v>2.0139999999999998</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H9" s="46"/>
       <c r="I9" s="25">
@@ -4438,7 +4475,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="44">
@@ -4450,7 +4487,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="46"/>
@@ -4466,25 +4503,25 @@
         <v>27</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="25">
+        <v>75</v>
+      </c>
+      <c r="E11" s="53">
         <v>0</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H11" s="47" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I11" s="25">
         <v>60</v>
@@ -4492,7 +4529,7 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="44">
@@ -4504,20 +4541,20 @@
         <v>27</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="25">
+        <v>79</v>
+      </c>
+      <c r="E12" s="53">
         <v>0</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H12" s="46"/>
       <c r="I12" s="25">
@@ -4526,7 +4563,7 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="44">
@@ -4538,20 +4575,20 @@
         <v>27</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="25">
+        <v>82</v>
+      </c>
+      <c r="E13" s="53">
         <v>0.92400000000000004</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" s="46"/>
       <c r="I13" s="25">
@@ -4560,7 +4597,7 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="44">
@@ -4572,7 +4609,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="53"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="46"/>
@@ -4588,23 +4625,23 @@
         <v>31</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="25">
+        <v>86</v>
+      </c>
+      <c r="E15" s="53">
         <v>0</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I15" s="25">
         <v>70</v>
@@ -4612,7 +4649,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="44">
@@ -4624,17 +4661,17 @@
         <v>31</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="25">
+        <v>90</v>
+      </c>
+      <c r="E16" s="53">
         <v>0.39300000000000002</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="46"/>
@@ -4644,7 +4681,7 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="44">
@@ -4656,7 +4693,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="46"/>
@@ -4672,23 +4709,23 @@
         <v>29</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D18" s="25">
         <v>1</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="53">
         <v>0</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="49" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I18" s="25">
         <v>80</v>
@@ -4708,17 +4745,17 @@
         <v>29</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="25">
         <v>2</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="53">
         <v>0</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="46"/>
@@ -4740,17 +4777,17 @@
         <v>29</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="25">
         <v>3</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="53">
         <v>0.64</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="46"/>
@@ -4772,17 +4809,17 @@
         <v>29</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="25">
         <v>4</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="53">
         <v>1.3129999999999999</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="46"/>
@@ -4804,7 +4841,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="53"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="46"/>
@@ -4820,23 +4857,23 @@
         <v>32</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="25">
+        <v>100</v>
+      </c>
+      <c r="E23" s="53">
         <v>0</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I23" s="25">
         <v>90</v>
@@ -4844,7 +4881,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="44">
@@ -4856,17 +4893,17 @@
         <v>32</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="25">
+        <v>103</v>
+      </c>
+      <c r="E24" s="53">
         <v>0.67800000000000005</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="46"/>
@@ -4876,11 +4913,105 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="44">
         <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="25">
+        <v>100</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="53">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="25">
+        <v>110</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="53">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="25">
+        <v>110</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="44">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4899,40 +5030,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75">
       <c r="A1" s="50" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D1" s="50" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E1" s="50" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F1" s="50" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -4940,7 +5071,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C2" s="51">
         <v>0</v>
@@ -4978,7 +5109,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C3" s="51">
         <v>0</v>
@@ -5016,7 +5147,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C4" s="51">
         <v>0</v>
@@ -5054,7 +5185,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C5" s="51">
         <v>0</v>
@@ -5092,7 +5223,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C6" s="51">
         <v>0</v>
@@ -5130,7 +5261,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C7" s="51">
         <v>0</v>
@@ -5168,7 +5299,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C8" s="51">
         <v>0</v>
@@ -5206,7 +5337,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C9" s="51">
         <v>0</v>
@@ -5244,7 +5375,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C10" s="51">
         <v>0</v>
@@ -5282,7 +5413,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C11" s="51">
         <v>0</v>
@@ -5320,7 +5451,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C12" s="51">
         <v>0</v>
@@ -5358,7 +5489,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C13" s="51">
         <v>0</v>
@@ -5396,7 +5527,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C14" s="51">
         <v>0</v>
@@ -5434,7 +5565,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C15" s="51">
         <v>0</v>
@@ -5472,7 +5603,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C16" s="51">
         <v>0</v>
@@ -5510,7 +5641,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C17" s="51">
         <v>0</v>
@@ -5548,7 +5679,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -5586,7 +5717,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C19" s="51">
         <v>0</v>
@@ -5624,7 +5755,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C20" s="51">
         <v>0</v>
@@ -5662,7 +5793,7 @@
         <v>44</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C21" s="51">
         <v>0</v>
@@ -5700,7 +5831,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C22" s="51">
         <v>0</v>
@@ -5738,7 +5869,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C23" s="51">
         <v>0</v>
@@ -5776,7 +5907,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C24" s="51">
         <v>0</v>
@@ -5814,7 +5945,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C25" s="51">
         <v>0</v>
@@ -5852,7 +5983,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
@@ -5890,7 +6021,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C27" s="51">
         <v>0</v>
@@ -5928,7 +6059,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C28" s="51">
         <v>0</v>
@@ -5966,7 +6097,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C29" s="51">
         <v>0</v>
@@ -6004,7 +6135,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C30" s="51">
         <v>0</v>
@@ -6042,7 +6173,7 @@
         <v>54</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C31" s="51">
         <v>0</v>
@@ -6080,7 +6211,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C32" s="51">
         <v>0</v>
@@ -6118,7 +6249,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C33" s="51">
         <v>0.01</v>
@@ -6156,7 +6287,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C34" s="51">
         <v>0.01</v>
@@ -6194,7 +6325,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C35" s="51">
         <v>0.01</v>
@@ -6232,7 +6363,7 @@
         <v>59</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C36" s="51">
         <v>0.01</v>
@@ -6270,7 +6401,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C37" s="51">
         <v>0.01</v>
@@ -6308,7 +6439,7 @@
         <v>61</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C38" s="51">
         <v>0.01</v>
@@ -6346,7 +6477,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C39" s="51">
         <v>0.01</v>
@@ -6384,7 +6515,7 @@
         <v>63</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C40" s="51">
         <v>0.01</v>
@@ -6422,7 +6553,7 @@
         <v>64</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C41" s="51">
         <v>0.01</v>
@@ -6460,7 +6591,7 @@
         <v>65</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C42" s="51">
         <v>0.01</v>
@@ -6498,7 +6629,7 @@
         <v>66</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C43" s="51">
         <v>0.01</v>
@@ -6536,7 +6667,7 @@
         <v>67</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C44" s="51">
         <v>0.01</v>
@@ -6574,7 +6705,7 @@
         <v>68</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C45" s="51">
         <v>0.02</v>
@@ -6612,7 +6743,7 @@
         <v>69</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C46" s="51">
         <v>0.02</v>
@@ -6650,7 +6781,7 @@
         <v>70</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C47" s="51">
         <v>0.02</v>
@@ -6688,7 +6819,7 @@
         <v>71</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C48" s="51">
         <v>0.02</v>
@@ -6726,7 +6857,7 @@
         <v>72</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C49" s="51">
         <v>0.02</v>
@@ -6764,7 +6895,7 @@
         <v>73</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C50" s="51">
         <v>0.02</v>
@@ -6802,7 +6933,7 @@
         <v>74</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C51" s="51">
         <v>0.03</v>
@@ -6840,7 +6971,7 @@
         <v>75</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C52" s="51">
         <v>0.03</v>
@@ -6878,7 +7009,7 @@
         <v>76</v>
       </c>
       <c r="B53" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C53" s="51">
         <v>0.03</v>
@@ -6916,7 +7047,7 @@
         <v>77</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C54" s="51">
         <v>0.04</v>
@@ -6954,7 +7085,7 @@
         <v>78</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C55" s="51">
         <v>0.04</v>
@@ -6992,7 +7123,7 @@
         <v>79</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C56" s="51">
         <v>0.05</v>
@@ -7030,7 +7161,7 @@
         <v>80</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C57" s="51">
         <v>0.05</v>
@@ -7068,7 +7199,7 @@
         <v>81</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C58" s="51">
         <v>0.06</v>
@@ -7106,7 +7237,7 @@
         <v>82</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C59" s="51">
         <v>7.0000000000000007E-2</v>
@@ -7144,7 +7275,7 @@
         <v>83</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C60" s="51">
         <v>7.0000000000000007E-2</v>
@@ -7182,7 +7313,7 @@
         <v>84</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C61" s="51">
         <v>0.08</v>
@@ -7220,7 +7351,7 @@
         <v>85</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C62" s="51">
         <v>0.09</v>
@@ -7258,7 +7389,7 @@
         <v>25</v>
       </c>
       <c r="B63" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C63" s="51">
         <v>0</v>
@@ -7296,7 +7427,7 @@
         <v>26</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C64" s="51">
         <v>0</v>
@@ -7334,7 +7465,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C65" s="51">
         <v>0</v>
@@ -7372,7 +7503,7 @@
         <v>28</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C66" s="51">
         <v>0</v>
@@ -7410,7 +7541,7 @@
         <v>29</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C67" s="51">
         <v>0</v>
@@ -7448,7 +7579,7 @@
         <v>30</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C68" s="51">
         <v>0</v>
@@ -7486,7 +7617,7 @@
         <v>31</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C69" s="51">
         <v>0</v>
@@ -7524,7 +7655,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C70" s="51">
         <v>0</v>
@@ -7562,7 +7693,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C71" s="51">
         <v>0</v>
@@ -7600,7 +7731,7 @@
         <v>34</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C72" s="51">
         <v>0</v>
@@ -7638,7 +7769,7 @@
         <v>35</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C73" s="51">
         <v>0</v>
@@ -7676,7 +7807,7 @@
         <v>36</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C74" s="51">
         <v>0</v>
@@ -7714,7 +7845,7 @@
         <v>37</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C75" s="51">
         <v>0</v>
@@ -7752,7 +7883,7 @@
         <v>38</v>
       </c>
       <c r="B76" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C76" s="51">
         <v>0</v>
@@ -7790,7 +7921,7 @@
         <v>39</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C77" s="51">
         <v>0</v>
@@ -7828,7 +7959,7 @@
         <v>40</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C78" s="51">
         <v>0</v>
@@ -7866,7 +7997,7 @@
         <v>41</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C79" s="51">
         <v>0</v>
@@ -7904,7 +8035,7 @@
         <v>42</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C80" s="51">
         <v>0</v>
@@ -7942,7 +8073,7 @@
         <v>43</v>
       </c>
       <c r="B81" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C81" s="51">
         <v>0</v>
@@ -7980,7 +8111,7 @@
         <v>44</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C82" s="51">
         <v>0</v>
@@ -8018,7 +8149,7 @@
         <v>45</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C83" s="51">
         <v>0</v>
@@ -8056,7 +8187,7 @@
         <v>46</v>
       </c>
       <c r="B84" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C84" s="51">
         <v>0</v>
@@ -8094,7 +8225,7 @@
         <v>47</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C85" s="51">
         <v>0</v>
@@ -8132,7 +8263,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C86" s="51">
         <v>0</v>
@@ -8170,7 +8301,7 @@
         <v>49</v>
       </c>
       <c r="B87" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C87" s="51">
         <v>0</v>
@@ -8208,7 +8339,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C88" s="51">
         <v>0</v>
@@ -8246,7 +8377,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C89" s="51">
         <v>0</v>
@@ -8284,7 +8415,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C90" s="51">
         <v>0</v>
@@ -8322,7 +8453,7 @@
         <v>53</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C91" s="51">
         <v>0</v>
@@ -8360,7 +8491,7 @@
         <v>54</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C92" s="51">
         <v>0</v>
@@ -8398,7 +8529,7 @@
         <v>55</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C93" s="51">
         <v>0</v>
@@ -8436,7 +8567,7 @@
         <v>56</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C94" s="51">
         <v>0</v>
@@ -8474,7 +8605,7 @@
         <v>57</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C95" s="51">
         <v>0</v>
@@ -8512,7 +8643,7 @@
         <v>58</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C96" s="51">
         <v>0</v>
@@ -8550,7 +8681,7 @@
         <v>59</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C97" s="51">
         <v>0</v>
@@ -8588,7 +8719,7 @@
         <v>60</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C98" s="51">
         <v>0</v>
@@ -8626,7 +8757,7 @@
         <v>61</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C99" s="51">
         <v>0.01</v>
@@ -8664,7 +8795,7 @@
         <v>62</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C100" s="51">
         <v>0.01</v>
@@ -8702,7 +8833,7 @@
         <v>63</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C101" s="51">
         <v>0.01</v>
@@ -8740,7 +8871,7 @@
         <v>64</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C102" s="51">
         <v>0.01</v>
@@ -8778,7 +8909,7 @@
         <v>65</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C103" s="51">
         <v>0.01</v>
@@ -8816,7 +8947,7 @@
         <v>66</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C104" s="51">
         <v>0.01</v>
@@ -8854,7 +8985,7 @@
         <v>67</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C105" s="51">
         <v>0.01</v>
@@ -8892,7 +9023,7 @@
         <v>68</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C106" s="51">
         <v>0.01</v>
@@ -8930,7 +9061,7 @@
         <v>69</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C107" s="51">
         <v>0.01</v>
@@ -8968,7 +9099,7 @@
         <v>70</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C108" s="51">
         <v>0.01</v>
@@ -9006,7 +9137,7 @@
         <v>71</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C109" s="51">
         <v>0.01</v>
@@ -9044,7 +9175,7 @@
         <v>72</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C110" s="51">
         <v>0.01</v>
@@ -9082,7 +9213,7 @@
         <v>73</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C111" s="51">
         <v>0.02</v>
@@ -9120,7 +9251,7 @@
         <v>74</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C112" s="51">
         <v>0.02</v>
@@ -9158,7 +9289,7 @@
         <v>75</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C113" s="51">
         <v>0.02</v>
@@ -9196,7 +9327,7 @@
         <v>76</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C114" s="51">
         <v>0.02</v>
@@ -9234,7 +9365,7 @@
         <v>77</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C115" s="51">
         <v>0.03</v>
@@ -9272,7 +9403,7 @@
         <v>78</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C116" s="51">
         <v>0.03</v>
@@ -9310,7 +9441,7 @@
         <v>79</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C117" s="51">
         <v>0.03</v>
@@ -9348,7 +9479,7 @@
         <v>80</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C118" s="51">
         <v>0.04</v>
@@ -9386,7 +9517,7 @@
         <v>81</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C119" s="51">
         <v>0.04</v>
@@ -9424,7 +9555,7 @@
         <v>82</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C120" s="51">
         <v>0.05</v>
@@ -9462,7 +9593,7 @@
         <v>83</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C121" s="51">
         <v>0.05</v>
@@ -9500,7 +9631,7 @@
         <v>84</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C122" s="51">
         <v>0.06</v>
@@ -9538,7 +9669,7 @@
         <v>85</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C123" s="51">
         <v>7.0000000000000007E-2</v>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28122"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F0C72ED-C198-4D55-8763-79CAA4ABE3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E85B90-2538-4DE0-8EDA-C110139F2379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="6" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="125">
   <si>
     <t>Notes</t>
   </si>
@@ -468,10 +468,37 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>:age-at-surgery</t>
+  </si>
+  <si>
+    <t>Age at surgery</t>
+  </si>
+  <si>
+    <t>:numeric</t>
+  </si>
+  <si>
+    <t>Age when the kidney cancer surgery was performed. An age between 25 and 85 may be entered here.</t>
+  </si>
+  <si>
+    <t>:sex</t>
+  </si>
+  <si>
+    <t>:male</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>:female</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
     <t>Age</t>
-  </si>
-  <si>
-    <t>Sex</t>
   </si>
   <si>
     <t>Year1</t>
@@ -4127,10 +4154,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
@@ -4883,6 +4910,98 @@
         <v>1</v>
       </c>
     </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="25">
+        <v>100</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="25"/>
+      <c r="F26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="25">
+        <v>110</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="25"/>
+      <c r="F27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="25">
+        <v>110</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="44">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181100000000002" footer="0.51181100000000002"/>
   <pageSetup orientation="portrait"/>
@@ -4899,40 +5018,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75">
       <c r="A1" s="50" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D1" s="50" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E1" s="50" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F1" s="50" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -4940,7 +5059,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C2" s="51">
         <v>0</v>
@@ -4978,7 +5097,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C3" s="51">
         <v>0</v>
@@ -5016,7 +5135,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C4" s="51">
         <v>0</v>
@@ -5054,7 +5173,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C5" s="51">
         <v>0</v>
@@ -5092,7 +5211,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C6" s="51">
         <v>0</v>
@@ -5130,7 +5249,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C7" s="51">
         <v>0</v>
@@ -5168,7 +5287,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C8" s="51">
         <v>0</v>
@@ -5206,7 +5325,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C9" s="51">
         <v>0</v>
@@ -5244,7 +5363,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C10" s="51">
         <v>0</v>
@@ -5282,7 +5401,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C11" s="51">
         <v>0</v>
@@ -5320,7 +5439,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C12" s="51">
         <v>0</v>
@@ -5358,7 +5477,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C13" s="51">
         <v>0</v>
@@ -5396,7 +5515,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C14" s="51">
         <v>0</v>
@@ -5434,7 +5553,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C15" s="51">
         <v>0</v>
@@ -5472,7 +5591,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C16" s="51">
         <v>0</v>
@@ -5510,7 +5629,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C17" s="51">
         <v>0</v>
@@ -5548,7 +5667,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -5586,7 +5705,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C19" s="51">
         <v>0</v>
@@ -5624,7 +5743,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C20" s="51">
         <v>0</v>
@@ -5662,7 +5781,7 @@
         <v>44</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C21" s="51">
         <v>0</v>
@@ -5700,7 +5819,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C22" s="51">
         <v>0</v>
@@ -5738,7 +5857,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C23" s="51">
         <v>0</v>
@@ -5776,7 +5895,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C24" s="51">
         <v>0</v>
@@ -5814,7 +5933,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C25" s="51">
         <v>0</v>
@@ -5852,7 +5971,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
@@ -5890,7 +6009,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C27" s="51">
         <v>0</v>
@@ -5928,7 +6047,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C28" s="51">
         <v>0</v>
@@ -5966,7 +6085,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C29" s="51">
         <v>0</v>
@@ -6004,7 +6123,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C30" s="51">
         <v>0</v>
@@ -6042,7 +6161,7 @@
         <v>54</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C31" s="51">
         <v>0</v>
@@ -6080,7 +6199,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C32" s="51">
         <v>0</v>
@@ -6118,7 +6237,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C33" s="51">
         <v>0.01</v>
@@ -6156,7 +6275,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C34" s="51">
         <v>0.01</v>
@@ -6194,7 +6313,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C35" s="51">
         <v>0.01</v>
@@ -6232,7 +6351,7 @@
         <v>59</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C36" s="51">
         <v>0.01</v>
@@ -6270,7 +6389,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C37" s="51">
         <v>0.01</v>
@@ -6308,7 +6427,7 @@
         <v>61</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C38" s="51">
         <v>0.01</v>
@@ -6346,7 +6465,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C39" s="51">
         <v>0.01</v>
@@ -6384,7 +6503,7 @@
         <v>63</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C40" s="51">
         <v>0.01</v>
@@ -6422,7 +6541,7 @@
         <v>64</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C41" s="51">
         <v>0.01</v>
@@ -6460,7 +6579,7 @@
         <v>65</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C42" s="51">
         <v>0.01</v>
@@ -6498,7 +6617,7 @@
         <v>66</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C43" s="51">
         <v>0.01</v>
@@ -6536,7 +6655,7 @@
         <v>67</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C44" s="51">
         <v>0.01</v>
@@ -6574,7 +6693,7 @@
         <v>68</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C45" s="51">
         <v>0.02</v>
@@ -6612,7 +6731,7 @@
         <v>69</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C46" s="51">
         <v>0.02</v>
@@ -6650,7 +6769,7 @@
         <v>70</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C47" s="51">
         <v>0.02</v>
@@ -6688,7 +6807,7 @@
         <v>71</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C48" s="51">
         <v>0.02</v>
@@ -6726,7 +6845,7 @@
         <v>72</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C49" s="51">
         <v>0.02</v>
@@ -6764,7 +6883,7 @@
         <v>73</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C50" s="51">
         <v>0.02</v>
@@ -6802,7 +6921,7 @@
         <v>74</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C51" s="51">
         <v>0.03</v>
@@ -6840,7 +6959,7 @@
         <v>75</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C52" s="51">
         <v>0.03</v>
@@ -6878,7 +6997,7 @@
         <v>76</v>
       </c>
       <c r="B53" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C53" s="51">
         <v>0.03</v>
@@ -6916,7 +7035,7 @@
         <v>77</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C54" s="51">
         <v>0.04</v>
@@ -6954,7 +7073,7 @@
         <v>78</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C55" s="51">
         <v>0.04</v>
@@ -6992,7 +7111,7 @@
         <v>79</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C56" s="51">
         <v>0.05</v>
@@ -7030,7 +7149,7 @@
         <v>80</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C57" s="51">
         <v>0.05</v>
@@ -7068,7 +7187,7 @@
         <v>81</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C58" s="51">
         <v>0.06</v>
@@ -7106,7 +7225,7 @@
         <v>82</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C59" s="51">
         <v>7.0000000000000007E-2</v>
@@ -7144,7 +7263,7 @@
         <v>83</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C60" s="51">
         <v>7.0000000000000007E-2</v>
@@ -7182,7 +7301,7 @@
         <v>84</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C61" s="51">
         <v>0.08</v>
@@ -7220,7 +7339,7 @@
         <v>85</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C62" s="51">
         <v>0.09</v>
@@ -7258,7 +7377,7 @@
         <v>25</v>
       </c>
       <c r="B63" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C63" s="51">
         <v>0</v>
@@ -7296,7 +7415,7 @@
         <v>26</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C64" s="51">
         <v>0</v>
@@ -7334,7 +7453,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C65" s="51">
         <v>0</v>
@@ -7372,7 +7491,7 @@
         <v>28</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C66" s="51">
         <v>0</v>
@@ -7410,7 +7529,7 @@
         <v>29</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C67" s="51">
         <v>0</v>
@@ -7448,7 +7567,7 @@
         <v>30</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C68" s="51">
         <v>0</v>
@@ -7486,7 +7605,7 @@
         <v>31</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C69" s="51">
         <v>0</v>
@@ -7524,7 +7643,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C70" s="51">
         <v>0</v>
@@ -7562,7 +7681,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C71" s="51">
         <v>0</v>
@@ -7600,7 +7719,7 @@
         <v>34</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C72" s="51">
         <v>0</v>
@@ -7638,7 +7757,7 @@
         <v>35</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C73" s="51">
         <v>0</v>
@@ -7676,7 +7795,7 @@
         <v>36</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C74" s="51">
         <v>0</v>
@@ -7714,7 +7833,7 @@
         <v>37</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C75" s="51">
         <v>0</v>
@@ -7752,7 +7871,7 @@
         <v>38</v>
       </c>
       <c r="B76" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C76" s="51">
         <v>0</v>
@@ -7790,7 +7909,7 @@
         <v>39</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C77" s="51">
         <v>0</v>
@@ -7828,7 +7947,7 @@
         <v>40</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C78" s="51">
         <v>0</v>
@@ -7866,7 +7985,7 @@
         <v>41</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C79" s="51">
         <v>0</v>
@@ -7904,7 +8023,7 @@
         <v>42</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C80" s="51">
         <v>0</v>
@@ -7942,7 +8061,7 @@
         <v>43</v>
       </c>
       <c r="B81" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C81" s="51">
         <v>0</v>
@@ -7980,7 +8099,7 @@
         <v>44</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C82" s="51">
         <v>0</v>
@@ -8018,7 +8137,7 @@
         <v>45</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C83" s="51">
         <v>0</v>
@@ -8056,7 +8175,7 @@
         <v>46</v>
       </c>
       <c r="B84" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C84" s="51">
         <v>0</v>
@@ -8094,7 +8213,7 @@
         <v>47</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C85" s="51">
         <v>0</v>
@@ -8132,7 +8251,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C86" s="51">
         <v>0</v>
@@ -8170,7 +8289,7 @@
         <v>49</v>
       </c>
       <c r="B87" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C87" s="51">
         <v>0</v>
@@ -8208,7 +8327,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C88" s="51">
         <v>0</v>
@@ -8246,7 +8365,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C89" s="51">
         <v>0</v>
@@ -8284,7 +8403,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C90" s="51">
         <v>0</v>
@@ -8322,7 +8441,7 @@
         <v>53</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C91" s="51">
         <v>0</v>
@@ -8360,7 +8479,7 @@
         <v>54</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C92" s="51">
         <v>0</v>
@@ -8398,7 +8517,7 @@
         <v>55</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C93" s="51">
         <v>0</v>
@@ -8436,7 +8555,7 @@
         <v>56</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C94" s="51">
         <v>0</v>
@@ -8474,7 +8593,7 @@
         <v>57</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C95" s="51">
         <v>0</v>
@@ -8512,7 +8631,7 @@
         <v>58</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C96" s="51">
         <v>0</v>
@@ -8550,7 +8669,7 @@
         <v>59</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C97" s="51">
         <v>0</v>
@@ -8588,7 +8707,7 @@
         <v>60</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C98" s="51">
         <v>0</v>
@@ -8626,7 +8745,7 @@
         <v>61</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C99" s="51">
         <v>0.01</v>
@@ -8664,7 +8783,7 @@
         <v>62</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C100" s="51">
         <v>0.01</v>
@@ -8702,7 +8821,7 @@
         <v>63</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C101" s="51">
         <v>0.01</v>
@@ -8740,7 +8859,7 @@
         <v>64</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C102" s="51">
         <v>0.01</v>
@@ -8778,7 +8897,7 @@
         <v>65</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C103" s="51">
         <v>0.01</v>
@@ -8816,7 +8935,7 @@
         <v>66</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C104" s="51">
         <v>0.01</v>
@@ -8854,7 +8973,7 @@
         <v>67</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C105" s="51">
         <v>0.01</v>
@@ -8892,7 +9011,7 @@
         <v>68</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C106" s="51">
         <v>0.01</v>
@@ -8930,7 +9049,7 @@
         <v>69</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C107" s="51">
         <v>0.01</v>
@@ -8968,7 +9087,7 @@
         <v>70</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C108" s="51">
         <v>0.01</v>
@@ -9006,7 +9125,7 @@
         <v>71</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C109" s="51">
         <v>0.01</v>
@@ -9044,7 +9163,7 @@
         <v>72</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C110" s="51">
         <v>0.01</v>
@@ -9082,7 +9201,7 @@
         <v>73</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C111" s="51">
         <v>0.02</v>
@@ -9120,7 +9239,7 @@
         <v>74</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C112" s="51">
         <v>0.02</v>
@@ -9158,7 +9277,7 @@
         <v>75</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C113" s="51">
         <v>0.02</v>
@@ -9196,7 +9315,7 @@
         <v>76</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C114" s="51">
         <v>0.02</v>
@@ -9234,7 +9353,7 @@
         <v>77</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C115" s="51">
         <v>0.03</v>
@@ -9272,7 +9391,7 @@
         <v>78</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C116" s="51">
         <v>0.03</v>
@@ -9310,7 +9429,7 @@
         <v>79</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C117" s="51">
         <v>0.03</v>
@@ -9348,7 +9467,7 @@
         <v>80</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C118" s="51">
         <v>0.04</v>
@@ -9386,7 +9505,7 @@
         <v>81</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C119" s="51">
         <v>0.04</v>
@@ -9424,7 +9543,7 @@
         <v>82</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C120" s="51">
         <v>0.05</v>
@@ -9462,7 +9581,7 @@
         <v>83</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C121" s="51">
         <v>0.05</v>
@@ -9500,7 +9619,7 @@
         <v>84</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C122" s="51">
         <v>0.06</v>
@@ -9538,7 +9657,7 @@
         <v>85</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C123" s="51">
         <v>7.0000000000000007E-2</v>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28122"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E85B90-2538-4DE0-8EDA-C110139F2379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B3CED99-68A8-4EDB-973B-6A58D5EE0448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="6" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="125">
   <si>
     <t>Notes</t>
   </si>
@@ -474,7 +474,7 @@
     <t>Age at surgery</t>
   </si>
   <si>
-    <t>:numeric</t>
+    <t>{:dps 1, :max 85, :min 25, :type :numeric}</t>
   </si>
   <si>
     <t>Age when the kidney cancer surgery was performed. An age between 25 and 85 may be entered here.</t>
@@ -483,7 +483,7 @@
     <t>:sex</t>
   </si>
   <si>
-    <t>:male</t>
+    <t>:Male</t>
   </si>
   <si>
     <t>Sex</t>
@@ -492,7 +492,7 @@
     <t>Male</t>
   </si>
   <si>
-    <t>:female</t>
+    <t>:Female</t>
   </si>
   <si>
     <t>Female</t>
@@ -772,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -857,6 +857,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4229,7 +4231,7 @@
       <c r="D2" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="43">
+      <c r="E2" s="52">
         <v>0</v>
       </c>
       <c r="F2" s="42" t="s">
@@ -4265,7 +4267,7 @@
       <c r="D3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="53">
         <v>1.2430000000000001</v>
       </c>
       <c r="F3" s="4"/>
@@ -4296,7 +4298,7 @@
       <c r="D4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="53">
         <v>1.6479999999999999</v>
       </c>
       <c r="F4" s="4"/>
@@ -4327,7 +4329,7 @@
       <c r="D5" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="53">
         <v>1.6479999999999999</v>
       </c>
       <c r="F5" s="4"/>
@@ -4358,7 +4360,7 @@
       <c r="D6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="53">
         <v>1.8959999999999999</v>
       </c>
       <c r="F6" s="4"/>
@@ -4389,7 +4391,7 @@
       <c r="D7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="53">
         <v>2.0139999999999998</v>
       </c>
       <c r="F7" s="4"/>
@@ -4420,7 +4422,7 @@
       <c r="D8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="53">
         <v>2.0139999999999998</v>
       </c>
       <c r="F8" s="4"/>
@@ -4451,7 +4453,7 @@
       <c r="D9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="53">
         <v>2.0139999999999998</v>
       </c>
       <c r="F9" s="4"/>
@@ -4477,7 +4479,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="46"/>
@@ -4501,7 +4503,7 @@
       <c r="D11" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="53">
         <v>0</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -4537,7 +4539,7 @@
       <c r="D12" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="53">
         <v>0</v>
       </c>
       <c r="F12" s="9" t="s">
@@ -4571,7 +4573,7 @@
       <c r="D13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="53">
         <v>0.92400000000000004</v>
       </c>
       <c r="F13" s="9" t="s">
@@ -4599,7 +4601,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="53"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="46"/>
@@ -4623,7 +4625,7 @@
       <c r="D15" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="53">
         <v>0</v>
       </c>
       <c r="F15" s="9" t="s">
@@ -4657,7 +4659,7 @@
       <c r="D16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="53">
         <v>0.39300000000000002</v>
       </c>
       <c r="F16" s="9" t="s">
@@ -4683,7 +4685,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="46"/>
@@ -4707,7 +4709,7 @@
       <c r="D18" s="25">
         <v>1</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="53">
         <v>0</v>
       </c>
       <c r="F18" s="9" t="s">
@@ -4741,7 +4743,7 @@
       <c r="D19" s="25">
         <v>2</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="53">
         <v>0</v>
       </c>
       <c r="F19" s="9" t="s">
@@ -4773,7 +4775,7 @@
       <c r="D20" s="25">
         <v>3</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="53">
         <v>0.64</v>
       </c>
       <c r="F20" s="9" t="s">
@@ -4805,7 +4807,7 @@
       <c r="D21" s="25">
         <v>4</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="53">
         <v>1.3129999999999999</v>
       </c>
       <c r="F21" s="9" t="s">
@@ -4831,7 +4833,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="53"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="46"/>
@@ -4855,7 +4857,7 @@
       <c r="D23" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="53">
         <v>0</v>
       </c>
       <c r="F23" s="9" t="s">
@@ -4889,7 +4891,7 @@
       <c r="D24" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="53">
         <v>0.67800000000000005</v>
       </c>
       <c r="F24" s="9" t="s">
@@ -4919,7 +4921,7 @@
         <v>103</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="25"/>
+      <c r="E25" s="53"/>
       <c r="F25" s="9" t="s">
         <v>104</v>
       </c>
@@ -4951,7 +4953,9 @@
       <c r="D26" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="25"/>
+      <c r="E26" s="53">
+        <v>0</v>
+      </c>
       <c r="F26" s="9" t="s">
         <v>47</v>
       </c>
@@ -4977,13 +4981,13 @@
       <c r="B27" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>108</v>
-      </c>
+      <c r="C27" s="9"/>
       <c r="D27" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="25"/>
+      <c r="E27" s="53">
+        <v>0</v>
+      </c>
       <c r="F27" s="9" t="s">
         <v>47</v>
       </c>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28122"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B3CED99-68A8-4EDB-973B-6A58D5EE0448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC96DAE6-98D9-4359-982B-8F5B874E7E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
     <t>Age at surgery</t>
   </si>
   <si>
-    <t>{:dps 1, :max 85, :min 25, :type :numeric}</t>
+    <t>{:dps 0, :max 85, :min 25, :type :numeric}</t>
   </si>
   <si>
     <t>Age when the kidney cancer surgery was performed. An age between 25 and 85 may be entered here.</t>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28409"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9D096E1-1831-45A5-8C56-572661716DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F150EB0C-282B-4FF8-9A48-0C23826D5C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
   </si>
   <si>
     <t>[:div "The pathological stage of a kidney cancer tumour is a measure of its size and how far it has spread. This is determined by assessing cancer tissue removed during surgery."
-   [:ul
+   [:ul { :class-name "more-info-list" }
       [:li "Stage 1a (or pT1a) – the cancer is small (4cm or smaller) and only inside the kidney"]
       [:li "Stage 1b (or pT1b) – the cancer is small (between 4cm and 7 cm) and only inside the kidney"]
       [:li "Stage 2a (pT2a) - the cancer is between 7cm and 10cm and only inside the kidney"]
@@ -288,8 +288,8 @@
     <t>there were no lymph nodes found in the tumour samples removed at the time of surgery</t>
   </si>
   <si>
-    <t>[:div "The regional lymph node status indicates if the cancer has spread to lymph nodes near the kidney. Lymph nodes are a network of glands found throughout the body that drain away waste products and fight infections. Lymph nodes near the kidney may be removed during surgery and tested for the presence of cancer."   
-    [:ul
+    <t>[:div "The regional lymph node status indicates if the cancer has spread to lymph nodes near the kidney. Lymph nodes are a network of glands found throughout the body that drain away waste products and fight infections. Lymph nodes near the kidney may be removed during surgery and tested for the presence of cancer.  However, it is common for no lymph nodes to be removed at the time of surgery and no further investigation to be required."
+    [:ul  { :class-name "more-info-list" }
         [:li "No investigation required (pNx) - There were no lymph nodes in the tissue removed at surgery. This is common if there are no noticeable lymph nodes present."]
         [:li "pN0 – No cancer was detected in any lymph nodes near the tumour."]
         [:li "pN1 – Cancer cells were detected in one or more lymph nodes near the tumour."]]

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp2\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6675DE73-B5EB-4C30-B086-82ADE3F8FFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546D93B7-7C2D-4E7C-9D5C-A33B537C3C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -14033,7 +14033,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="9" t="s">
@@ -14064,7 +14064,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="9" t="s">
@@ -14095,7 +14095,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="9" t="s">

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F150EB0C-282B-4FF8-9A48-0C23826D5C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp2\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6675DE73-B5EB-4C30-B086-82ADE3F8FFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -15,6 +20,10 @@
     <sheet name="ldsurvival-baseline-vars" sheetId="5" r:id="rId5"/>
     <sheet name="ldsurvival-inputs" sheetId="6" r:id="rId6"/>
     <sheet name="ldsurvival-competing-mortality" sheetId="7" r:id="rId7"/>
+    <sheet name="pkm-baseline-vars" sheetId="11" r:id="rId8"/>
+    <sheet name="pkm-inputs" sheetId="8" r:id="rId9"/>
+    <sheet name="pkm-baseline-hazards-mort" sheetId="9" r:id="rId10"/>
+    <sheet name="pkm-baseline-hazards-rcc" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="148">
   <si>
     <t>Notes</t>
   </si>
@@ -87,6 +96,7 @@
         <sz val="12"/>
         <color indexed="13"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.openstreetmap.org/#map=6/54.910/-3.432</t>
     </r>
@@ -334,6 +344,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>"The size of the kidney cancer tumour removed during surgery."</t>
     </r>
@@ -342,6 +353,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>]</t>
     </r>
@@ -370,6 +382,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[:p </t>
     </r>
@@ -378,6 +391,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>"The nuclear grade is a scale indicating</t>
     </r>
@@ -386,6 +400,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> how much the cancer cells look like
 normal cells. This is sometimes called the Fuhrman scale.
@@ -396,6 +411,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -405,6 +421,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>Kidney cancers are graded 1 to 4. Grade 1 is the lowest (the most like normal cells) and grade 4 is the highest (the least like normal cells). Higher grade cancers tend to grow
 more quickly and are more likely to spread to other parts of the body.</t>
@@ -414,6 +431,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>"</t>
     </r>
@@ -422,6 +440,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>]</t>
     </r>
@@ -450,6 +469,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">[:p </t>
     </r>
@@ -458,6 +478,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>"The tumour necrosis indicates if dead cancer cells were found in the samples removed at surgery. Dead cells may indicate a faster-growing tumour. If necrosis was detected the cancer is more likely to return."</t>
     </r>
@@ -466,6 +487,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
       </rPr>
       <t>]</t>
     </r>
@@ -539,6 +561,98 @@
   <si>
     <t>F</t>
   </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>[:div "The pathological stage of a kidney cancer tumour is a measure of its size and how far it has spread. This is determined by assessing cancer tissue removed during surgery. "
+   [:ul { :class-name "more-info-list" }
+      [:li "Stage 1 (or pT1) - the cancer is small (&lt;7cm) and only inside the kidney"]
+      [:li "Stage 2 (or pT2) - the cancer is larger (&gt;7cm) and only inside the kidney"]
+      [:li "Stage 3 (or pT3) - that cancer is growing into the area surrounding the kidney (this can include growing into the fat around the kidney, the renal vein or the vena cava)"]
+      [:li "Stage 4 (or pT4) - the cancer has spread through the capsule that surrounds the kidney. It may have grown into the adrenal gland."]]
+]</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>:charlson-comorbidity-score</t>
+  </si>
+  <si>
+    <t>Charlson comorbidity score</t>
+  </si>
+  <si>
+    <t>{:dps 0, :max 31, :min 2, :type :numeric}</t>
+  </si>
+  <si>
+    <t>:smoking-history</t>
+  </si>
+  <si>
+    <t>Smoking history</t>
+  </si>
+  <si>
+    <t>Current tobacco use</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[:p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Smoking history at the time of surgery. Patients with a history of tobacco usage are more at risk of other long-term health conditions and are relatively less likely to die from kidney cancer."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>Former tobacco use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never Used Tobacco </t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>H0</t>
+  </si>
+  <si>
+    <t>9.73061225351342e-05</t>
+  </si>
+  <si>
+    <t>:pkm</t>
+  </si>
+  <si>
+    <t>:Current</t>
+  </si>
+  <si>
+    <t>:Former</t>
+  </si>
+  <si>
+    <t>:Never</t>
+  </si>
 </sst>
 </file>
 
@@ -547,7 +661,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
@@ -557,42 +671,50 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color indexed="13"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="14"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -604,6 +726,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -775,7 +903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -862,6 +990,21 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2005,12 +2148,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="44" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.6640625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="1"/>
+    <col min="3" max="6" width="8.6328125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -2111,22 +2254,3958 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8E1BF3-41AF-4E29-BE72-1191A068E638}">
+  <dimension ref="A1:C178"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.33</v>
+      </c>
+      <c r="C2">
+        <v>-2.33784229721341E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.42</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>4.4005943062052499E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C5">
+        <v>7.9458261596456305E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.67</v>
+      </c>
+      <c r="C6">
+        <v>1.1606956400157899E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0.75</v>
+      </c>
+      <c r="C7">
+        <v>1.53807000407422E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0.83</v>
+      </c>
+      <c r="C8">
+        <v>1.9269356608526899E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.92</v>
+      </c>
+      <c r="C9">
+        <v>2.3273990606751398E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2.7392981028955799E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1.08</v>
+      </c>
+      <c r="C11">
+        <v>3.16259846513069E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>3.5973238419070002E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1.25</v>
+      </c>
+      <c r="C13">
+        <v>4.0435842948066602E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1.33</v>
+      </c>
+      <c r="C14">
+        <v>4.5013932408218098E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1.42</v>
+      </c>
+      <c r="C15">
+        <v>4.9706790880517503E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1.5</v>
+      </c>
+      <c r="C16">
+        <v>5.4514394331581202E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1.58</v>
+      </c>
+      <c r="C17">
+        <v>5.9436718728025596E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1.67</v>
+      </c>
+      <c r="C18">
+        <v>6.4473740036467102E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1.75</v>
+      </c>
+      <c r="C19">
+        <v>6.9625434223522104E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1.83</v>
+      </c>
+      <c r="C20">
+        <v>7.4891777255807002E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1.92</v>
+      </c>
+      <c r="C21">
+        <v>8.0272745099938293E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>8.5768313722532196E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>2.08</v>
+      </c>
+      <c r="C23">
+        <v>9.1378459090205293E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>2.17</v>
+      </c>
+      <c r="C24">
+        <v>9.7103157169573899E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>2.25</v>
+      </c>
+      <c r="C25">
+        <v>1.02942383927254E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>2.33</v>
+      </c>
+      <c r="C26">
+        <v>1.08896115329863E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>2.42</v>
+      </c>
+      <c r="C27">
+        <v>1.14964327344017E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>2.5</v>
+      </c>
+      <c r="C28">
+        <v>1.2114699593633101E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>2.58</v>
+      </c>
+      <c r="C29">
+        <v>1.2744486556468501E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>2.67</v>
+      </c>
+      <c r="C30">
+        <v>1.33857125982526E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>2.75</v>
+      </c>
+      <c r="C31">
+        <v>1.40382282314574E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>2.83</v>
+      </c>
+      <c r="C32">
+        <v>1.4702068525414801E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>2.92</v>
+      </c>
+      <c r="C33">
+        <v>1.53772624026732E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>1.60638387857811E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>3.08</v>
+      </c>
+      <c r="C35">
+        <v>1.6761826597287002E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>3.17</v>
+      </c>
+      <c r="C36">
+        <v>1.7471254759739301E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>3.25</v>
+      </c>
+      <c r="C37">
+        <v>1.8192152195686401E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>3.33</v>
+      </c>
+      <c r="C38">
+        <v>1.8924547827676799E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>3.42</v>
+      </c>
+      <c r="C39">
+        <v>1.9668470578258899E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>3.5</v>
+      </c>
+      <c r="C40">
+        <v>2.0423949369981199E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>3.58</v>
+      </c>
+      <c r="C41">
+        <v>2.1191067258620699E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>3.67</v>
+      </c>
+      <c r="C42">
+        <v>2.19699105119774E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>3.75</v>
+      </c>
+      <c r="C43">
+        <v>2.2760407314445098E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>3.83</v>
+      </c>
+      <c r="C44">
+        <v>2.3562586763419699E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>3.92</v>
+      </c>
+      <c r="C45">
+        <v>2.43764779562969E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>2.5202109990472701E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>4.08</v>
+      </c>
+      <c r="C47">
+        <v>2.6039511963342799E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>4.17</v>
+      </c>
+      <c r="C48">
+        <v>2.6888712972303101E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>4.25</v>
+      </c>
+      <c r="C49">
+        <v>2.7749742114749301E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>4.33</v>
+      </c>
+      <c r="C50">
+        <v>2.8622545669070201E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>4.42</v>
+      </c>
+      <c r="C51">
+        <v>2.9504930622902301E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>4.5</v>
+      </c>
+      <c r="C52">
+        <v>3.0396208506444301E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>4.58</v>
+      </c>
+      <c r="C53">
+        <v>3.1296779663301702E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>4.67</v>
+      </c>
+      <c r="C54">
+        <v>3.22070444370803E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>4.75</v>
+      </c>
+      <c r="C55">
+        <v>3.3127403171385697E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>4.83</v>
+      </c>
+      <c r="C56">
+        <v>3.4058256209823397E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>4.92</v>
+      </c>
+      <c r="C57">
+        <v>3.50000038959992E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58">
+        <v>3.5953046573518603E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>5.08</v>
+      </c>
+      <c r="C59">
+        <v>3.6917784585987302E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>5.17</v>
+      </c>
+      <c r="C60">
+        <v>3.7894618277010801E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>5.25</v>
+      </c>
+      <c r="C61">
+        <v>3.88839479901949E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>5.33</v>
+      </c>
+      <c r="C62">
+        <v>3.9886174069145103E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>5.42</v>
+      </c>
+      <c r="C63">
+        <v>4.0901696857467099E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>5.5</v>
+      </c>
+      <c r="C64">
+        <v>4.1930916698766502E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>5.58</v>
+      </c>
+      <c r="C65">
+        <v>4.2974233936648898E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>5.67</v>
+      </c>
+      <c r="C66">
+        <v>4.4032048914719998E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>5.75</v>
+      </c>
+      <c r="C67">
+        <v>4.5103412779630203E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>5.83</v>
+      </c>
+      <c r="C68">
+        <v>4.6183594981779402E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>5.92</v>
+      </c>
+      <c r="C69">
+        <v>4.7272694510949897E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>6</v>
+      </c>
+      <c r="C70">
+        <v>4.8371338267846002E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>6.08</v>
+      </c>
+      <c r="C71">
+        <v>4.9480153153171801E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>6.17</v>
+      </c>
+      <c r="C72">
+        <v>5.05997660676318E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>6.25</v>
+      </c>
+      <c r="C73">
+        <v>5.17308039119301E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>6.33</v>
+      </c>
+      <c r="C74">
+        <v>5.2873893586770901E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>6.42</v>
+      </c>
+      <c r="C75">
+        <v>5.4029661992858601E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>6.5</v>
+      </c>
+      <c r="C76">
+        <v>5.5198737998598098E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>6.58</v>
+      </c>
+      <c r="C77">
+        <v>5.6381846312814003E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>6.67</v>
+      </c>
+      <c r="C78">
+        <v>5.7579507718747001E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>6.75</v>
+      </c>
+      <c r="C79">
+        <v>5.8792346734713098E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>6.83</v>
+      </c>
+      <c r="C80">
+        <v>6.0020987879028098E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>6.92</v>
+      </c>
+      <c r="C81">
+        <v>6.1266353617958701E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7</v>
+      </c>
+      <c r="C82">
+        <v>6.2528838150313001E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7.08</v>
+      </c>
+      <c r="C83">
+        <v>6.3809034668283901E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7.17</v>
+      </c>
+      <c r="C84">
+        <v>6.5107310464656301E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7.25</v>
+      </c>
+      <c r="C85">
+        <v>6.6415165691804695E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7.33</v>
+      </c>
+      <c r="C86">
+        <v>6.7729084593013494E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7.42</v>
+      </c>
+      <c r="C87">
+        <v>6.9050222257461394E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7.5</v>
+      </c>
+      <c r="C88">
+        <v>7.0379733774326797E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7.58</v>
+      </c>
+      <c r="C89">
+        <v>7.1718774232788302E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7.67</v>
+      </c>
+      <c r="C90">
+        <v>7.3068498722024394E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7.75</v>
+      </c>
+      <c r="C91">
+        <v>7.4430062331213895E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7.83</v>
+      </c>
+      <c r="C92">
+        <v>7.5804620149535096E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7.92</v>
+      </c>
+      <c r="C93">
+        <v>7.7193327266166595E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>8</v>
+      </c>
+      <c r="C94">
+        <v>7.8597338770287004E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>8.08</v>
+      </c>
+      <c r="C95">
+        <v>8.0017809751074906E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>8.17</v>
+      </c>
+      <c r="C96">
+        <v>8.1455895297708802E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>8.25</v>
+      </c>
+      <c r="C97">
+        <v>8.2912750499367305E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>8.33</v>
+      </c>
+      <c r="C98">
+        <v>8.4389530445228997E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>8.42</v>
+      </c>
+      <c r="C99">
+        <v>8.5887390224472296E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>8.5</v>
+      </c>
+      <c r="C100">
+        <v>8.74074849262758E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>8.58</v>
+      </c>
+      <c r="C101">
+        <v>8.8950969639818203E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>8.67</v>
+      </c>
+      <c r="C102">
+        <v>9.0518999454277896E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>8.75</v>
+      </c>
+      <c r="C103">
+        <v>9.2111646870125005E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>8.83</v>
+      </c>
+      <c r="C104">
+        <v>9.3724171658465499E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>8.92</v>
+      </c>
+      <c r="C105">
+        <v>9.5355660809412796E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>9</v>
+      </c>
+      <c r="C106">
+        <v>9.7005875105942205E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>9.08</v>
+      </c>
+      <c r="C107">
+        <v>9.8674575331028899E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>9.17</v>
+      </c>
+      <c r="C108">
+        <v>0.100361522267648</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>9.25</v>
+      </c>
+      <c r="C109">
+        <v>0.102066476698775</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>9.33</v>
+      </c>
+      <c r="C110">
+        <v>0.103789199407385</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>9.42</v>
+      </c>
+      <c r="C111">
+        <v>0.105529451176452</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>9.5</v>
+      </c>
+      <c r="C112">
+        <v>0.107286992788954</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>9.58</v>
+      </c>
+      <c r="C113">
+        <v>0.10906158502786301</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>9.67</v>
+      </c>
+      <c r="C114">
+        <v>0.11085298867615601</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>9.75</v>
+      </c>
+      <c r="C115">
+        <v>0.112660964516809</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>9.83</v>
+      </c>
+      <c r="C116">
+        <v>0.114485273332795</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>9.92</v>
+      </c>
+      <c r="C117">
+        <v>0.116325675907091</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>10</v>
+      </c>
+      <c r="C118">
+        <v>0.11818193302267101</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>10.08</v>
+      </c>
+      <c r="C119">
+        <v>0.120053805462511</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>10.17</v>
+      </c>
+      <c r="C120">
+        <v>0.12194105400958501</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>10.25</v>
+      </c>
+      <c r="C121">
+        <v>0.12384343944687</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>10.33</v>
+      </c>
+      <c r="C122">
+        <v>0.12576072255734</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>10.42</v>
+      </c>
+      <c r="C123">
+        <v>0.12769266412397101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>10.5</v>
+      </c>
+      <c r="C124">
+        <v>0.129639024929738</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>10.58</v>
+      </c>
+      <c r="C125">
+        <v>0.13159957096260799</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>10.67</v>
+      </c>
+      <c r="C126">
+        <v>0.133575559726824</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>10.75</v>
+      </c>
+      <c r="C127">
+        <v>0.13556804376472001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>10.83</v>
+      </c>
+      <c r="C128">
+        <v>0.137576948927492</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>10.92</v>
+      </c>
+      <c r="C129">
+        <v>0.139602201066336</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>11</v>
+      </c>
+      <c r="C130">
+        <v>0.14164372603244699</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>11.08</v>
+      </c>
+      <c r="C131">
+        <v>0.143701449677021</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>11.17</v>
+      </c>
+      <c r="C132">
+        <v>0.14577529785125401</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>11.25</v>
+      </c>
+      <c r="C133">
+        <v>0.14786519640634299</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>11.33</v>
+      </c>
+      <c r="C134">
+        <v>0.14997107119348199</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>11.42</v>
+      </c>
+      <c r="C135">
+        <v>0.152092848063869</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>11.5</v>
+      </c>
+      <c r="C136">
+        <v>0.15423045286869799</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>11.58</v>
+      </c>
+      <c r="C137">
+        <v>0.15638381145916699</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>11.67</v>
+      </c>
+      <c r="C138">
+        <v>0.15855284968646999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>11.75</v>
+      </c>
+      <c r="C139">
+        <v>0.16073749340180399</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>11.83</v>
+      </c>
+      <c r="C140">
+        <v>0.16293766845636401</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>11.92</v>
+      </c>
+      <c r="C141">
+        <v>0.16515330070134601</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>12</v>
+      </c>
+      <c r="C142">
+        <v>0.16738431598794801</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>12.08</v>
+      </c>
+      <c r="C143">
+        <v>0.16963064016736301</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>12.17</v>
+      </c>
+      <c r="C144">
+        <v>0.17189219909078801</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>12.25</v>
+      </c>
+      <c r="C145">
+        <v>0.17416891860941999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>12.33</v>
+      </c>
+      <c r="C146">
+        <v>0.176460724574454</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>12.42</v>
+      </c>
+      <c r="C147">
+        <v>0.17876754283708499</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>12.5</v>
+      </c>
+      <c r="C148">
+        <v>0.181089299248511</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>12.58</v>
+      </c>
+      <c r="C149">
+        <v>0.183425919659926</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>12.67</v>
+      </c>
+      <c r="C150">
+        <v>0.18577752871827299</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>12.75</v>
+      </c>
+      <c r="C151">
+        <v>0.188144502358286</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>12.83</v>
+      </c>
+      <c r="C152">
+        <v>0.19052685255995999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>12.92</v>
+      </c>
+      <c r="C153">
+        <v>0.192924579373214</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>13</v>
+      </c>
+      <c r="C154">
+        <v>0.19533768284796901</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>13.08</v>
+      </c>
+      <c r="C155">
+        <v>0.19776616303414399</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>13.17</v>
+      </c>
+      <c r="C156">
+        <v>0.20021001998165799</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>13.25</v>
+      </c>
+      <c r="C157">
+        <v>0.20266925374043199</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>13.33</v>
+      </c>
+      <c r="C158">
+        <v>0.20514386436038501</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>13.42</v>
+      </c>
+      <c r="C159">
+        <v>0.20763385189143499</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>13.5</v>
+      </c>
+      <c r="C160">
+        <v>0.210139216383504</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>13.58</v>
+      </c>
+      <c r="C161">
+        <v>0.21265995788650999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>13.67</v>
+      </c>
+      <c r="C162">
+        <v>0.215196076450374</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>13.75</v>
+      </c>
+      <c r="C163">
+        <v>0.217747572125014</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>13.83</v>
+      </c>
+      <c r="C164">
+        <v>0.22031444496035099</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>13.92</v>
+      </c>
+      <c r="C165">
+        <v>0.22289669500630399</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>14</v>
+      </c>
+      <c r="C166">
+        <v>0.22549432231279201</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>14.08</v>
+      </c>
+      <c r="C167">
+        <v>0.22810732692973601</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>14.17</v>
+      </c>
+      <c r="C168">
+        <v>0.230735708907054</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>14.25</v>
+      </c>
+      <c r="C169">
+        <v>0.23337946829466699</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>14.33</v>
+      </c>
+      <c r="C170">
+        <v>0.236038605142495</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>14.42</v>
+      </c>
+      <c r="C171">
+        <v>0.23871311950045501</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>14.5</v>
+      </c>
+      <c r="C172">
+        <v>0.24140301141847001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>14.58</v>
+      </c>
+      <c r="C173">
+        <v>0.24410828094645701</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>14.67</v>
+      </c>
+      <c r="C174">
+        <v>0.24682892813433599</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>14.75</v>
+      </c>
+      <c r="C175">
+        <v>0.249564953032028</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>14.83</v>
+      </c>
+      <c r="C176">
+        <v>0.25231635568945099</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>14.92</v>
+      </c>
+      <c r="C177">
+        <v>0.255083136156526</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>15</v>
+      </c>
+      <c r="C178">
+        <v>0.25786529448317203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBCBBD-4EFD-4108-87D7-F00F3581F55B}">
+  <dimension ref="A1:C178"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.33</v>
+      </c>
+      <c r="C2">
+        <v>9.18823222982017E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.42</v>
+      </c>
+      <c r="C3">
+        <v>1.97525779578097E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>3.0268744998106002E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C5">
+        <v>4.0778958047578001E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.67</v>
+      </c>
+      <c r="C6">
+        <v>5.1186609113149399E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0.75</v>
+      </c>
+      <c r="C7">
+        <v>6.1533159195875896E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0.83</v>
+      </c>
+      <c r="C8">
+        <v>7.18708600934164E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.92</v>
+      </c>
+      <c r="C9">
+        <v>8.2134864868256396E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>9.2345921724006994E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1.08</v>
+      </c>
+      <c r="C11">
+        <v>1.0252711562159299E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1.17</v>
+      </c>
+      <c r="C12">
+        <v>1.1267155027053499E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1.25</v>
+      </c>
+      <c r="C13">
+        <v>1.2276586025475E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1.33</v>
+      </c>
+      <c r="C14">
+        <v>1.32793802908857E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1.42</v>
+      </c>
+      <c r="C15">
+        <v>1.42764949631817E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1.5</v>
+      </c>
+      <c r="C16">
+        <v>1.5268610240862601E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1.58</v>
+      </c>
+      <c r="C17">
+        <v>1.6255701057490399E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1.67</v>
+      </c>
+      <c r="C18">
+        <v>1.7237742346626998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1.75</v>
+      </c>
+      <c r="C19">
+        <v>1.82147090418344E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1.83</v>
+      </c>
+      <c r="C20">
+        <v>1.91865760766745E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1.92</v>
+      </c>
+      <c r="C21">
+        <v>2.0153318384709198E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>2.1114910899500398E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>2.08</v>
+      </c>
+      <c r="C23">
+        <v>2.2071328554610099E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>2.17</v>
+      </c>
+      <c r="C24">
+        <v>2.30225462836002E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>2.25</v>
+      </c>
+      <c r="C25">
+        <v>2.3968539020032702E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>2.33</v>
+      </c>
+      <c r="C26">
+        <v>2.4909281697469501E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>2.42</v>
+      </c>
+      <c r="C27">
+        <v>2.5844749249472401E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>2.5</v>
+      </c>
+      <c r="C28">
+        <v>2.6774916609603499E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>2.58</v>
+      </c>
+      <c r="C29">
+        <v>2.7699758711424698E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>2.67</v>
+      </c>
+      <c r="C30">
+        <v>2.86192453813136E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>2.75</v>
+      </c>
+      <c r="C31">
+        <v>2.9532421877299202E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>2.83</v>
+      </c>
+      <c r="C32">
+        <v>3.04387947189429E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>2.92</v>
+      </c>
+      <c r="C33">
+        <v>3.1338655190494398E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>3.22322945762036E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>3.08</v>
+      </c>
+      <c r="C35">
+        <v>3.3120004160320501E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>3.17</v>
+      </c>
+      <c r="C36">
+        <v>3.4002075227094801E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>3.25</v>
+      </c>
+      <c r="C37">
+        <v>3.4878799060776497E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>3.33</v>
+      </c>
+      <c r="C38">
+        <v>3.5750466945615303E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>3.42</v>
+      </c>
+      <c r="C39">
+        <v>3.66173701658613E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>3.5</v>
+      </c>
+      <c r="C40">
+        <v>3.7479800005764098E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>3.58</v>
+      </c>
+      <c r="C41">
+        <v>3.8338047749573702E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>3.67</v>
+      </c>
+      <c r="C42">
+        <v>3.9192404681539998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>3.75</v>
+      </c>
+      <c r="C43">
+        <v>4.0043162085912798E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>3.83</v>
+      </c>
+      <c r="C44">
+        <v>4.0890611246942002E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>3.92</v>
+      </c>
+      <c r="C45">
+        <v>4.17350434488774E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>4.25767499759689E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>4.08</v>
+      </c>
+      <c r="C47">
+        <v>4.3416022112466403E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>4.17</v>
+      </c>
+      <c r="C48">
+        <v>4.4253151142619802E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>4.25</v>
+      </c>
+      <c r="C49">
+        <v>4.5088428350678798E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>4.33</v>
+      </c>
+      <c r="C50">
+        <v>4.5921717513721899E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>4.42</v>
+      </c>
+      <c r="C51">
+        <v>4.6741773036680298E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>4.5</v>
+      </c>
+      <c r="C52">
+        <v>4.7544941109773198E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>4.58</v>
+      </c>
+      <c r="C53">
+        <v>4.8333161053669901E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>4.67</v>
+      </c>
+      <c r="C54">
+        <v>4.9108372189039802E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>4.75</v>
+      </c>
+      <c r="C55">
+        <v>4.9872513836552203E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>4.83</v>
+      </c>
+      <c r="C56">
+        <v>5.0627525316876601E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>4.92</v>
+      </c>
+      <c r="C57">
+        <v>5.1375345950682397E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58">
+        <v>5.2117915058638803E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>5.08</v>
+      </c>
+      <c r="C59">
+        <v>5.28571719614154E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>5.17</v>
+      </c>
+      <c r="C60">
+        <v>5.3595055979681498E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>5.25</v>
+      </c>
+      <c r="C61">
+        <v>5.4333506434106497E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>5.33</v>
+      </c>
+      <c r="C62">
+        <v>5.5074462645359701E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>5.42</v>
+      </c>
+      <c r="C63">
+        <v>5.5819863934110703E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>5.5</v>
+      </c>
+      <c r="C64">
+        <v>5.6571649621028598E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>5.58</v>
+      </c>
+      <c r="C65">
+        <v>5.7331759026782898E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>5.67</v>
+      </c>
+      <c r="C66">
+        <v>5.81053075807237E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>5.75</v>
+      </c>
+      <c r="C67">
+        <v>5.8887254502336998E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>5.83</v>
+      </c>
+      <c r="C68">
+        <v>5.9662005287629903E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>5.92</v>
+      </c>
+      <c r="C69">
+        <v>6.0429240130904602E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>6</v>
+      </c>
+      <c r="C70">
+        <v>6.1190294952568398E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>6.08</v>
+      </c>
+      <c r="C71">
+        <v>6.1946505673028701E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>6.17</v>
+      </c>
+      <c r="C72">
+        <v>6.2699208212692897E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>6.25</v>
+      </c>
+      <c r="C73">
+        <v>6.3449738491968305E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>6.33</v>
+      </c>
+      <c r="C74">
+        <v>6.4199432431262402E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>6.42</v>
+      </c>
+      <c r="C75">
+        <v>6.4949625950982401E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>6.5</v>
+      </c>
+      <c r="C76">
+        <v>6.5701654971535794E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>6.58</v>
+      </c>
+      <c r="C77">
+        <v>6.6456089289370496E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>6.67</v>
+      </c>
+      <c r="C78">
+        <v>6.7213528264511893E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>6.75</v>
+      </c>
+      <c r="C79">
+        <v>6.7976641148640896E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>6.83</v>
+      </c>
+      <c r="C80">
+        <v>6.8746747034192507E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>6.92</v>
+      </c>
+      <c r="C81">
+        <v>6.95251650136018E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7</v>
+      </c>
+      <c r="C82">
+        <v>7.0313214179303904E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7.08</v>
+      </c>
+      <c r="C83">
+        <v>7.1112213623733905E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7.17</v>
+      </c>
+      <c r="C84">
+        <v>7.1923407192064706E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7.25</v>
+      </c>
+      <c r="C85">
+        <v>7.27449362473232E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7.33</v>
+      </c>
+      <c r="C86">
+        <v>7.3574910211740605E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7.42</v>
+      </c>
+      <c r="C87">
+        <v>7.4412546057013404E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7.5</v>
+      </c>
+      <c r="C88">
+        <v>7.5257060754838206E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7.58</v>
+      </c>
+      <c r="C89">
+        <v>7.6107671276911606E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7.67</v>
+      </c>
+      <c r="C90">
+        <v>7.6963594594930101E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7.75</v>
+      </c>
+      <c r="C91">
+        <v>7.7824047680590494E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7.83</v>
+      </c>
+      <c r="C92">
+        <v>7.8688247505589004E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7.92</v>
+      </c>
+      <c r="C93">
+        <v>7.9555411041622504E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>8</v>
+      </c>
+      <c r="C94">
+        <v>8.0424755260387407E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>8.08</v>
+      </c>
+      <c r="C95">
+        <v>8.1295497133580405E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>8.17</v>
+      </c>
+      <c r="C96">
+        <v>8.2166853632897899E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>8.25</v>
+      </c>
+      <c r="C97">
+        <v>8.3038041730036705E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>8.33</v>
+      </c>
+      <c r="C98">
+        <v>8.3908278396693195E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>8.42</v>
+      </c>
+      <c r="C99">
+        <v>8.4776780604564103E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>8.5</v>
+      </c>
+      <c r="C100">
+        <v>8.5642765325345899E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>8.58</v>
+      </c>
+      <c r="C101">
+        <v>8.6505449530735204E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>8.67</v>
+      </c>
+      <c r="C102">
+        <v>8.7364050192428502E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>8.75</v>
+      </c>
+      <c r="C103">
+        <v>8.8219443890173901E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>8.83</v>
+      </c>
+      <c r="C104">
+        <v>8.90791416558568E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>8.92</v>
+      </c>
+      <c r="C105">
+        <v>8.9943738198434098E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>9</v>
+      </c>
+      <c r="C106">
+        <v>9.0812732884303998E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>9.08</v>
+      </c>
+      <c r="C107">
+        <v>9.1685625079864802E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>9.17</v>
+      </c>
+      <c r="C108">
+        <v>9.2561914151514602E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>9.25</v>
+      </c>
+      <c r="C109">
+        <v>9.3441099465651795E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>9.33</v>
+      </c>
+      <c r="C110">
+        <v>9.4322680388674404E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>9.42</v>
+      </c>
+      <c r="C111">
+        <v>9.52061562869808E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>9.5</v>
+      </c>
+      <c r="C112">
+        <v>9.60910265269692E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>9.58</v>
+      </c>
+      <c r="C113">
+        <v>9.6976790475037697E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>9.67</v>
+      </c>
+      <c r="C114">
+        <v>9.7862947497584604E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>9.75</v>
+      </c>
+      <c r="C115">
+        <v>9.8748996961008195E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>9.83</v>
+      </c>
+      <c r="C116">
+        <v>9.9634438231706604E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>9.92</v>
+      </c>
+      <c r="C117">
+        <v>0.10051877067607801</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>10</v>
+      </c>
+      <c r="C118">
+        <v>0.10140149366052099</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>10.08</v>
+      </c>
+      <c r="C119">
+        <v>0.10228627862676699</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>10.17</v>
+      </c>
+      <c r="C120">
+        <v>0.10317101839943001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>10.25</v>
+      </c>
+      <c r="C121">
+        <v>0.104052810173629</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>10.33</v>
+      </c>
+      <c r="C122">
+        <v>0.104931158883764</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>10.42</v>
+      </c>
+      <c r="C123">
+        <v>0.105805569464235</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>10.5</v>
+      </c>
+      <c r="C124">
+        <v>0.106675546849442</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>10.58</v>
+      </c>
+      <c r="C125">
+        <v>0.107540606779474</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>10.67</v>
+      </c>
+      <c r="C126">
+        <v>0.10840338162888299</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>10.75</v>
+      </c>
+      <c r="C127">
+        <v>0.109266149668337</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>10.83</v>
+      </c>
+      <c r="C128">
+        <v>0.110128865833745</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>10.92</v>
+      </c>
+      <c r="C129">
+        <v>0.110991485061018</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>11</v>
+      </c>
+      <c r="C130">
+        <v>0.11185396228606399</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>11.08</v>
+      </c>
+      <c r="C131">
+        <v>0.112716252444793</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>11.17</v>
+      </c>
+      <c r="C132">
+        <v>0.11357831047311299</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>11.25</v>
+      </c>
+      <c r="C133">
+        <v>0.114440091306933</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>11.33</v>
+      </c>
+      <c r="C134">
+        <v>0.115301549882164</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>11.42</v>
+      </c>
+      <c r="C135">
+        <v>0.116162641134713</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>11.5</v>
+      </c>
+      <c r="C136">
+        <v>0.117023320000491</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>11.58</v>
+      </c>
+      <c r="C137">
+        <v>0.117883541415406</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>11.67</v>
+      </c>
+      <c r="C138">
+        <v>0.118743260315368</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>11.75</v>
+      </c>
+      <c r="C139">
+        <v>0.11960243163628501</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>11.83</v>
+      </c>
+      <c r="C140">
+        <v>0.120461010314067</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>11.92</v>
+      </c>
+      <c r="C141">
+        <v>0.121318951284622</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>12</v>
+      </c>
+      <c r="C142">
+        <v>0.122176209483861</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>12.08</v>
+      </c>
+      <c r="C143">
+        <v>0.123028894480653</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>12.17</v>
+      </c>
+      <c r="C144">
+        <v>0.123878209435722</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>12.25</v>
+      </c>
+      <c r="C145">
+        <v>0.124726562005335</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>12.33</v>
+      </c>
+      <c r="C146">
+        <v>0.12557324535761899</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>12.42</v>
+      </c>
+      <c r="C147">
+        <v>0.126418742833357</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>12.5</v>
+      </c>
+      <c r="C148">
+        <v>0.12726319650243401</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>12.58</v>
+      </c>
+      <c r="C149">
+        <v>0.128106562470925</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>12.67</v>
+      </c>
+      <c r="C150">
+        <v>0.12894894523856101</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>12.75</v>
+      </c>
+      <c r="C151">
+        <v>0.129790632412147</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>12.83</v>
+      </c>
+      <c r="C152">
+        <v>0.130631636167204</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>12.92</v>
+      </c>
+      <c r="C153">
+        <v>0.13147195971870901</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>13</v>
+      </c>
+      <c r="C154">
+        <v>0.13231160628163799</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>13.08</v>
+      </c>
+      <c r="C155">
+        <v>0.133150579070968</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>13.17</v>
+      </c>
+      <c r="C156">
+        <v>0.13398888130167599</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>13.25</v>
+      </c>
+      <c r="C157">
+        <v>0.134826516188739</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>13.33</v>
+      </c>
+      <c r="C158">
+        <v>0.13566348694713401</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>13.42</v>
+      </c>
+      <c r="C159">
+        <v>0.13649979679183599</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>13.5</v>
+      </c>
+      <c r="C160">
+        <v>0.13733544893782301</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>13.58</v>
+      </c>
+      <c r="C161">
+        <v>0.13817044660007199</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>13.67</v>
+      </c>
+      <c r="C162">
+        <v>0.139004792993559</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>13.75</v>
+      </c>
+      <c r="C163">
+        <v>0.13983849133326201</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>13.83</v>
+      </c>
+      <c r="C164">
+        <v>0.140671544834156</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>13.92</v>
+      </c>
+      <c r="C165">
+        <v>0.14150395671121899</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>14</v>
+      </c>
+      <c r="C166">
+        <v>0.14233573017942699</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>14.08</v>
+      </c>
+      <c r="C167">
+        <v>0.14316686845375801</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>14.17</v>
+      </c>
+      <c r="C168">
+        <v>0.143997374749187</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>14.25</v>
+      </c>
+      <c r="C169">
+        <v>0.14482725228069199</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>14.33</v>
+      </c>
+      <c r="C170">
+        <v>0.145656504263249</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>14.42</v>
+      </c>
+      <c r="C171">
+        <v>0.14648513391183601</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>14.5</v>
+      </c>
+      <c r="C172">
+        <v>0.14731886923898899</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>14.58</v>
+      </c>
+      <c r="C173">
+        <v>0.14815440275193201</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>14.67</v>
+      </c>
+      <c r="C174">
+        <v>0.14898593420337899</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>14.75</v>
+      </c>
+      <c r="C175">
+        <v>0.14981203052717201</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>14.83</v>
+      </c>
+      <c r="C176">
+        <v>0.15063746489782501</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>14.92</v>
+      </c>
+      <c r="C177">
+        <v>0.15146224127060701</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>15</v>
+      </c>
+      <c r="C178">
+        <v>0.15228256046564201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.44140625" style="1"/>
+    <col min="1" max="1" width="8.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.4" customHeight="1">
+    <row r="1" spans="1:6" ht="15.45" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
@@ -2146,7 +6225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.45" customHeight="1">
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>12</v>
       </c>
@@ -2245,14 +6324,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.44140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.44140625" style="1"/>
+    <col min="1" max="1" width="7.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.453125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -2282,9 +6361,15 @@
       <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="A3" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>20</v>
+      </c>
       <c r="D3" s="4"/>
       <c r="E3" s="16"/>
     </row>
@@ -2349,13 +6434,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E203"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="8.44140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.44140625" style="1"/>
+    <col min="1" max="1" width="14.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="8.453125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.453125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -4044,12 +8129,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.44140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.44140625" style="1"/>
+    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
+    <col min="3" max="6" width="8.453125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.453125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -4168,21 +8253,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" style="1" customWidth="1"/>
     <col min="7" max="7" width="81" style="1" customWidth="1"/>
-    <col min="8" max="8" width="116.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.21875" style="1" customWidth="1"/>
-    <col min="10" max="12" width="14.21875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="40.33203125" style="1" customWidth="1"/>
-    <col min="14" max="15" width="8.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.44140625" style="1"/>
+    <col min="8" max="8" width="116.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1796875" style="1" customWidth="1"/>
+    <col min="10" max="12" width="14.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="40.36328125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="8.453125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.453125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.100000000000001" customHeight="1">
@@ -4229,7 +8314,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="156.94999999999999" customHeight="1">
+    <row r="2" spans="1:14" ht="156.9" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>30</v>
       </c>
@@ -4855,7 +8940,7 @@
       <c r="M22" s="4"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="1:14" ht="45.4" customHeight="1">
+    <row r="23" spans="1:14" ht="45.45" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -5031,7 +9116,7 @@
   <dimension ref="A1:L123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75">
+    <row r="1" spans="1:12">
       <c r="A1" s="50" t="s">
         <v>113</v>
       </c>
@@ -9703,6 +13788,997 @@
       </c>
       <c r="L123" s="51">
         <v>0.74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD640821-0FB9-4D59-BBAC-F550C45F339E}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
+    <col min="3" max="6" width="8.453125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.453125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A1" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A2" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A3" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A4" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A5" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A6" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A7" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A8" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A9" s="61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5" ht="17.100000000000001" customHeight="1">
+      <c r="A10" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="61"/>
+      <c r="C10" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181100000000002" footer="0.51181100000000002"/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261E92C2-54DD-4827-851F-385906BB591F}">
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="81" style="1" customWidth="1"/>
+    <col min="8" max="8" width="116.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1796875" style="1" customWidth="1"/>
+    <col min="10" max="12" width="14.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="40.36328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.453125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A1" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" s="41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="156.9" customHeight="1">
+      <c r="A2" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="52">
+        <v>0</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="43">
+        <v>50</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="23"/>
+      <c r="N2" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="53">
+        <v>1.2430000000000001</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="25">
+        <v>50</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="53">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="25">
+        <v>50</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="53">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="25">
+        <v>50</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="1:14" ht="126" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="53">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="25">
+        <v>60</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="53">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="46"/>
+      <c r="I8" s="25">
+        <v>60</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="53">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="46"/>
+      <c r="I9" s="25">
+        <v>60</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="16"/>
+    </row>
+    <row r="11" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="53">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="25">
+        <v>70</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="53">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="25">
+        <v>70</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" ht="119.25" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1</v>
+      </c>
+      <c r="E14" s="53">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="25">
+        <v>80</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="25">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="25">
+        <v>2</v>
+      </c>
+      <c r="E15" s="53">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="25">
+        <v>80</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="25">
+        <v>2</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="25">
+        <v>3</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0.64</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="25">
+        <v>80</v>
+      </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="25">
+        <v>3</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="N16" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="25">
+        <v>4</v>
+      </c>
+      <c r="E17" s="53">
+        <v>1.3129999999999999</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="25">
+        <v>80</v>
+      </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="25">
+        <v>4</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="16"/>
+    </row>
+    <row r="19" spans="1:14" ht="45.45" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="53">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="25">
+        <v>90</v>
+      </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="M19" s="4"/>
+      <c r="N19" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="53">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="25">
+        <v>90</v>
+      </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="4"/>
+      <c r="N20" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="25">
+        <v>100</v>
+      </c>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="53">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="25">
+        <v>110</v>
+      </c>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="M22" s="4"/>
+      <c r="N22" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="53">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="25">
+        <v>110</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M23" s="4"/>
+      <c r="N23" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="25">
+        <v>120</v>
+      </c>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30">
+      <c r="A25" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="53">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" s="25">
+        <v>130</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="25">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4"/>
+      <c r="N25" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="53">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="25">
+        <v>130</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="25">
+        <v>2</v>
+      </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="53">
+        <v>2</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="25">
+        <v>130</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="25">
+        <v>3</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="44">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56A9581-4766-4D3C-9198-22122D9BB762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40964FC5-6DA5-4991-B335-CA27030D669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15285" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -689,12 +689,6 @@
     </r>
   </si>
   <si>
-    <t>[:div
-  [:p "The Charlson Comorbidity Score is a measure of the number and severity of long-term conditions present for an individual. It includes 15 conditions in addition to cancer. Details of how this calculated can be found in the technical section."]
-  [:p "A high Charlson Score indicates that a patient is frail and less likely to benefit from further treatment for kidney cancer."]
-]</t>
-  </si>
-  <si>
     <t>[:p "Age when the kidney cancer surgery was performed. Older patients are more at risk of other long-term health conditions and are relatively less likely to die from kidney cancer. An age between 25 and 85 may be entered here."]</t>
   </si>
   <si>
@@ -702,6 +696,11 @@
   </si>
   <si>
     <t>{:dps 0, :max 31, :min 2, :type :numeric :validation "Score must be between 2 and 31"  :calc-workflow :charlson}</t>
+  </si>
+  <si>
+    <t>[:p [:span "The Charlson Comorbidity Score is a measure of the number and severity of long-term conditions present for an individual."
+[:span {:class-name "d-print-none" } " It includes 15 conditions in addition to cancer. Details of how this calculated can be found in the technical section."]
+" A high Charlson Score indicates that a patient is frail and less likely to benefit from further treatment for kidney cancer."]]</t>
   </si>
   <si>
     <t>Never used tobacco</t>
@@ -9079,11 +9078,11 @@
       <c r="D25" s="9"/>
       <c r="E25" s="53"/>
       <c r="F25" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I25" s="25">
         <v>100</v>
@@ -14630,11 +14629,11 @@
       <c r="D21" s="9"/>
       <c r="E21" s="53"/>
       <c r="F21" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I21" s="25">
         <v>100</v>
@@ -14724,11 +14723,11 @@
       <c r="D24" s="9"/>
       <c r="E24" s="53"/>
       <c r="F24" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="49" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I24" s="25">
         <v>120</v>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp2\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546D93B7-7C2D-4E7C-9D5C-A33B537C3C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217B294A-7196-43DD-95BD-C45F3F20F84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="151">
   <si>
     <t>Notes</t>
   </si>
@@ -505,9 +505,6 @@
     <t>{:dps 0, :max 85, :min 25, :type :numeric}</t>
   </si>
   <si>
-    <t>[:p "Age when the kidney cancer surgery was performed. An age between 25 and 85 may be entered here."]</t>
-  </si>
-  <si>
     <t>:Male</t>
   </si>
   <si>
@@ -563,15 +560,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>[:div "The pathological stage of a kidney cancer tumour is a measure of its size and how far it has spread. This is determined by assessing cancer tissue removed during surgery. "
-   [:ul { :class-name "more-info-list" }
-      [:li "Stage 1 (or pT1) - the cancer is small (&lt;7cm) and only inside the kidney"]
-      [:li "Stage 2 (or pT2) - the cancer is larger (&gt;7cm) and only inside the kidney"]
-      [:li "Stage 3 (or pT3) - that cancer is growing into the area surrounding the kidney (this can include growing into the fat around the kidney, the renal vein or the vena cava)"]
-      [:li "Stage 4 (or pT4) - the cancer has spread through the capsule that surrounds the kidney. It may have grown into the adrenal gland."]]
-]</t>
   </si>
   <si>
     <t>2</t>
@@ -652,6 +640,71 @@
   </si>
   <si>
     <t>:Never</t>
+  </si>
+  <si>
+    <t>[:div "The pathological stage of a kidney cancer tumour is a measure of its size and how far it has spread. This is determined by assessing cancer tissue removed during surgery. "
+   [:ul { :class-name "more-info-list" }
+      [:li "Stage 1 (or pT1) - the cancer is small (&lt;7cm) and only inside the kidney"]
+      [:li "Stage 2 (or pT2) - the cancer is larger (&gt;7cm) and only inside the kidney"]
+      [:li "Stage 3 (or pT3) - that cancer is growing into the area surrounding the kidney (this can include growing into the fat around the kidney, the renal vein or the vena cava)"]
+      [:li "Stage 4 (or pT4) - the cancer has spread through the capsule that surrounds the kidney. It may have grown into the adrenal gland."]]
+   "The model does not differentiate between stage sub-classifications (such as T2a or T2b)."
+]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[:p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>"The size of the kidney cancer tumour removed during surgery. This factor is not used in the PREDICT-Kidney model (and so will not affect the estimated risks). It is included in the tool as it used to calculate the Leibovich score and assess eligibility for adjuvant treatment."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[:p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>"The tumour necrosis indicates if dead cancer cells were found in the samples removed at surgery. Dead cells may indicate a faster-growing tumour. If necrosis was detected the cancer is more likely to return. This factor is not used in the PREDICT-Kidney model (and so will not affect the estimated risks). It is included in the tool as it used to calculate the Leibovich score and assess eligibility for adjuvant treatment."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>[:div
+  [:p "The Charlson Comorbidity Score is a measure of the number and severity of long-term conditions present for an individual. It includes 15 conditions in addition to cancer. Details of how this calculated can be found in the technical section."]
+  [:p "A high Charlson Score indicates that a patient is frail and less likely to benefit from further treatment for kidney cancer."]
+]</t>
+  </si>
+  <si>
+    <t>[:p "Age when the kidney cancer surgery was performed. Older patients are more at risk of other long-term health conditions and are relatively less likely to die from kidney cancer. An age between 25 and 85 may be entered here."]</t>
   </si>
 </sst>
 </file>
@@ -2261,13 +2314,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" t="s">
         <v>140</v>
-      </c>
-      <c r="B1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2289,7 +2342,7 @@
         <v>0.42</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4229,13 +4282,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" t="s">
         <v>140</v>
-      </c>
-      <c r="B1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6362,7 +6415,7 @@
     </row>
     <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>19</v>
@@ -9023,7 +9076,7 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="I25" s="25">
         <v>100</v>
@@ -9041,13 +9094,13 @@
         <v>34</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="E26" s="53">
         <v>0</v>
@@ -9063,7 +9116,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="44">
@@ -9075,11 +9128,11 @@
         <v>34</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E27" s="53">
         <v>0</v>
@@ -9095,7 +9148,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="44">
@@ -9118,40 +9171,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="50" t="s">
+      <c r="D1" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="E1" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="F1" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="G1" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="H1" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="I1" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="J1" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="K1" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="L1" s="50" t="s">
         <v>122</v>
-      </c>
-      <c r="L1" s="50" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -9159,7 +9212,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="51">
         <v>0</v>
@@ -9197,7 +9250,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="51">
         <v>0</v>
@@ -9235,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="51">
         <v>0</v>
@@ -9273,7 +9326,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="51">
         <v>0</v>
@@ -9311,7 +9364,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="51">
         <v>0</v>
@@ -9349,7 +9402,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="51">
         <v>0</v>
@@ -9387,7 +9440,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="51">
         <v>0</v>
@@ -9425,7 +9478,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="51">
         <v>0</v>
@@ -9463,7 +9516,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="51">
         <v>0</v>
@@ -9501,7 +9554,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="51">
         <v>0</v>
@@ -9539,7 +9592,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12" s="51">
         <v>0</v>
@@ -9577,7 +9630,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="51">
         <v>0</v>
@@ -9615,7 +9668,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="51">
         <v>0</v>
@@ -9653,7 +9706,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="51">
         <v>0</v>
@@ -9691,7 +9744,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="51">
         <v>0</v>
@@ -9729,7 +9782,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="51">
         <v>0</v>
@@ -9767,7 +9820,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -9805,7 +9858,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C19" s="51">
         <v>0</v>
@@ -9843,7 +9896,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="51">
         <v>0</v>
@@ -9881,7 +9934,7 @@
         <v>44</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" s="51">
         <v>0</v>
@@ -9919,7 +9972,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C22" s="51">
         <v>0</v>
@@ -9957,7 +10010,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C23" s="51">
         <v>0</v>
@@ -9995,7 +10048,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="51">
         <v>0</v>
@@ -10033,7 +10086,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="51">
         <v>0</v>
@@ -10071,7 +10124,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
@@ -10109,7 +10162,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27" s="51">
         <v>0</v>
@@ -10147,7 +10200,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="51">
         <v>0</v>
@@ -10185,7 +10238,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="51">
         <v>0</v>
@@ -10223,7 +10276,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" s="51">
         <v>0</v>
@@ -10261,7 +10314,7 @@
         <v>54</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" s="51">
         <v>0</v>
@@ -10299,7 +10352,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C32" s="51">
         <v>0</v>
@@ -10337,7 +10390,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C33" s="51">
         <v>0.01</v>
@@ -10375,7 +10428,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34" s="51">
         <v>0.01</v>
@@ -10413,7 +10466,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" s="51">
         <v>0.01</v>
@@ -10451,7 +10504,7 @@
         <v>59</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C36" s="51">
         <v>0.01</v>
@@ -10489,7 +10542,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37" s="51">
         <v>0.01</v>
@@ -10527,7 +10580,7 @@
         <v>61</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C38" s="51">
         <v>0.01</v>
@@ -10565,7 +10618,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C39" s="51">
         <v>0.01</v>
@@ -10603,7 +10656,7 @@
         <v>63</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C40" s="51">
         <v>0.01</v>
@@ -10641,7 +10694,7 @@
         <v>64</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="51">
         <v>0.01</v>
@@ -10679,7 +10732,7 @@
         <v>65</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C42" s="51">
         <v>0.01</v>
@@ -10717,7 +10770,7 @@
         <v>66</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C43" s="51">
         <v>0.01</v>
@@ -10755,7 +10808,7 @@
         <v>67</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C44" s="51">
         <v>0.01</v>
@@ -10793,7 +10846,7 @@
         <v>68</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C45" s="51">
         <v>0.02</v>
@@ -10831,7 +10884,7 @@
         <v>69</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C46" s="51">
         <v>0.02</v>
@@ -10869,7 +10922,7 @@
         <v>70</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47" s="51">
         <v>0.02</v>
@@ -10907,7 +10960,7 @@
         <v>71</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" s="51">
         <v>0.02</v>
@@ -10945,7 +10998,7 @@
         <v>72</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C49" s="51">
         <v>0.02</v>
@@ -10983,7 +11036,7 @@
         <v>73</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" s="51">
         <v>0.02</v>
@@ -11021,7 +11074,7 @@
         <v>74</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C51" s="51">
         <v>0.03</v>
@@ -11059,7 +11112,7 @@
         <v>75</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C52" s="51">
         <v>0.03</v>
@@ -11097,7 +11150,7 @@
         <v>76</v>
       </c>
       <c r="B53" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C53" s="51">
         <v>0.03</v>
@@ -11135,7 +11188,7 @@
         <v>77</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54" s="51">
         <v>0.04</v>
@@ -11173,7 +11226,7 @@
         <v>78</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C55" s="51">
         <v>0.04</v>
@@ -11211,7 +11264,7 @@
         <v>79</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C56" s="51">
         <v>0.05</v>
@@ -11249,7 +11302,7 @@
         <v>80</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C57" s="51">
         <v>0.05</v>
@@ -11287,7 +11340,7 @@
         <v>81</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58" s="51">
         <v>0.06</v>
@@ -11325,7 +11378,7 @@
         <v>82</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C59" s="51">
         <v>7.0000000000000007E-2</v>
@@ -11363,7 +11416,7 @@
         <v>83</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60" s="51">
         <v>7.0000000000000007E-2</v>
@@ -11401,7 +11454,7 @@
         <v>84</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C61" s="51">
         <v>0.08</v>
@@ -11439,7 +11492,7 @@
         <v>85</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C62" s="51">
         <v>0.09</v>
@@ -11477,7 +11530,7 @@
         <v>25</v>
       </c>
       <c r="B63" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C63" s="51">
         <v>0</v>
@@ -11515,7 +11568,7 @@
         <v>26</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C64" s="51">
         <v>0</v>
@@ -11553,7 +11606,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C65" s="51">
         <v>0</v>
@@ -11591,7 +11644,7 @@
         <v>28</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C66" s="51">
         <v>0</v>
@@ -11629,7 +11682,7 @@
         <v>29</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C67" s="51">
         <v>0</v>
@@ -11667,7 +11720,7 @@
         <v>30</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C68" s="51">
         <v>0</v>
@@ -11705,7 +11758,7 @@
         <v>31</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C69" s="51">
         <v>0</v>
@@ -11743,7 +11796,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C70" s="51">
         <v>0</v>
@@ -11781,7 +11834,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C71" s="51">
         <v>0</v>
@@ -11819,7 +11872,7 @@
         <v>34</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C72" s="51">
         <v>0</v>
@@ -11857,7 +11910,7 @@
         <v>35</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C73" s="51">
         <v>0</v>
@@ -11895,7 +11948,7 @@
         <v>36</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C74" s="51">
         <v>0</v>
@@ -11933,7 +11986,7 @@
         <v>37</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C75" s="51">
         <v>0</v>
@@ -11971,7 +12024,7 @@
         <v>38</v>
       </c>
       <c r="B76" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C76" s="51">
         <v>0</v>
@@ -12009,7 +12062,7 @@
         <v>39</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C77" s="51">
         <v>0</v>
@@ -12047,7 +12100,7 @@
         <v>40</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C78" s="51">
         <v>0</v>
@@ -12085,7 +12138,7 @@
         <v>41</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C79" s="51">
         <v>0</v>
@@ -12123,7 +12176,7 @@
         <v>42</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C80" s="51">
         <v>0</v>
@@ -12161,7 +12214,7 @@
         <v>43</v>
       </c>
       <c r="B81" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C81" s="51">
         <v>0</v>
@@ -12199,7 +12252,7 @@
         <v>44</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C82" s="51">
         <v>0</v>
@@ -12237,7 +12290,7 @@
         <v>45</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C83" s="51">
         <v>0</v>
@@ -12275,7 +12328,7 @@
         <v>46</v>
       </c>
       <c r="B84" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C84" s="51">
         <v>0</v>
@@ -12313,7 +12366,7 @@
         <v>47</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C85" s="51">
         <v>0</v>
@@ -12351,7 +12404,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C86" s="51">
         <v>0</v>
@@ -12389,7 +12442,7 @@
         <v>49</v>
       </c>
       <c r="B87" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C87" s="51">
         <v>0</v>
@@ -12427,7 +12480,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C88" s="51">
         <v>0</v>
@@ -12465,7 +12518,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C89" s="51">
         <v>0</v>
@@ -12503,7 +12556,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C90" s="51">
         <v>0</v>
@@ -12541,7 +12594,7 @@
         <v>53</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C91" s="51">
         <v>0</v>
@@ -12579,7 +12632,7 @@
         <v>54</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C92" s="51">
         <v>0</v>
@@ -12617,7 +12670,7 @@
         <v>55</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C93" s="51">
         <v>0</v>
@@ -12655,7 +12708,7 @@
         <v>56</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C94" s="51">
         <v>0</v>
@@ -12693,7 +12746,7 @@
         <v>57</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C95" s="51">
         <v>0</v>
@@ -12731,7 +12784,7 @@
         <v>58</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C96" s="51">
         <v>0</v>
@@ -12769,7 +12822,7 @@
         <v>59</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C97" s="51">
         <v>0</v>
@@ -12807,7 +12860,7 @@
         <v>60</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C98" s="51">
         <v>0</v>
@@ -12845,7 +12898,7 @@
         <v>61</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C99" s="51">
         <v>0.01</v>
@@ -12883,7 +12936,7 @@
         <v>62</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C100" s="51">
         <v>0.01</v>
@@ -12921,7 +12974,7 @@
         <v>63</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C101" s="51">
         <v>0.01</v>
@@ -12959,7 +13012,7 @@
         <v>64</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C102" s="51">
         <v>0.01</v>
@@ -12997,7 +13050,7 @@
         <v>65</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C103" s="51">
         <v>0.01</v>
@@ -13035,7 +13088,7 @@
         <v>66</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C104" s="51">
         <v>0.01</v>
@@ -13073,7 +13126,7 @@
         <v>67</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C105" s="51">
         <v>0.01</v>
@@ -13111,7 +13164,7 @@
         <v>68</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C106" s="51">
         <v>0.01</v>
@@ -13149,7 +13202,7 @@
         <v>69</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C107" s="51">
         <v>0.01</v>
@@ -13187,7 +13240,7 @@
         <v>70</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C108" s="51">
         <v>0.01</v>
@@ -13225,7 +13278,7 @@
         <v>71</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C109" s="51">
         <v>0.01</v>
@@ -13263,7 +13316,7 @@
         <v>72</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C110" s="51">
         <v>0.01</v>
@@ -13301,7 +13354,7 @@
         <v>73</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C111" s="51">
         <v>0.02</v>
@@ -13339,7 +13392,7 @@
         <v>74</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C112" s="51">
         <v>0.02</v>
@@ -13377,7 +13430,7 @@
         <v>75</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C113" s="51">
         <v>0.02</v>
@@ -13415,7 +13468,7 @@
         <v>76</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C114" s="51">
         <v>0.02</v>
@@ -13453,7 +13506,7 @@
         <v>77</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C115" s="51">
         <v>0.03</v>
@@ -13491,7 +13544,7 @@
         <v>78</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C116" s="51">
         <v>0.03</v>
@@ -13529,7 +13582,7 @@
         <v>79</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C117" s="51">
         <v>0.03</v>
@@ -13567,7 +13620,7 @@
         <v>80</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C118" s="51">
         <v>0.04</v>
@@ -13605,7 +13658,7 @@
         <v>81</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C119" s="51">
         <v>0.04</v>
@@ -13643,7 +13696,7 @@
         <v>82</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C120" s="51">
         <v>0.05</v>
@@ -13681,7 +13734,7 @@
         <v>83</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C121" s="51">
         <v>0.05</v>
@@ -13719,7 +13772,7 @@
         <v>84</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C122" s="51">
         <v>0.06</v>
@@ -13757,7 +13810,7 @@
         <v>85</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C123" s="51">
         <v>7.0000000000000007E-2</v>
@@ -13898,7 +13951,7 @@
     </row>
     <row r="9" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="61" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" s="61"/>
       <c r="C9" s="62" t="s">
@@ -13909,7 +13962,7 @@
     </row>
     <row r="10" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A10" s="61" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" s="61"/>
       <c r="C10" s="62" t="s">
@@ -14001,7 +14054,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E2" s="52">
         <v>0</v>
@@ -14013,7 +14066,7 @@
         <v>50</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="I2" s="43">
         <v>50</v>
@@ -14037,7 +14090,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E3" s="53">
         <v>1.2430000000000001</v>
@@ -14068,7 +14121,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="53">
         <v>1.6479999999999999</v>
@@ -14099,7 +14152,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E5" s="53">
         <v>1.6479999999999999</v>
@@ -14280,7 +14333,7 @@
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="48" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="I11" s="25">
         <v>70</v>
@@ -14512,7 +14565,7 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="49" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="I19" s="25">
         <v>90</v>
@@ -14574,7 +14627,7 @@
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="49" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="I21" s="25">
         <v>100</v>
@@ -14592,13 +14645,13 @@
         <v>34</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="E22" s="53">
         <v>0</v>
@@ -14614,7 +14667,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="44">
@@ -14626,11 +14679,11 @@
         <v>34</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="53">
         <v>0</v>
@@ -14646,7 +14699,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="44">
@@ -14655,20 +14708,20 @@
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="53"/>
       <c r="F24" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="49" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="I24" s="25">
         <v>120</v>
@@ -14683,16 +14736,16 @@
     </row>
     <row r="25" spans="1:14" ht="30">
       <c r="A25" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="25" t="s">
         <v>134</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>136</v>
       </c>
       <c r="E25" s="53">
         <v>0</v>
@@ -14702,7 +14755,7 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I25" s="25">
         <v>130</v>
@@ -14719,14 +14772,14 @@
     </row>
     <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E26" s="53">
         <v>1</v>
@@ -14751,14 +14804,14 @@
     </row>
     <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E27" s="53">
         <v>2</v>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp2\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217B294A-7196-43DD-95BD-C45F3F20F84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD51361-C56E-4901-AD12-A9B8DCCF674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -502,9 +502,6 @@
     <t>Age at surgery</t>
   </si>
   <si>
-    <t>{:dps 0, :max 85, :min 25, :type :numeric}</t>
-  </si>
-  <si>
     <t>:Male</t>
   </si>
   <si>
@@ -575,9 +572,6 @@
   </si>
   <si>
     <t>Charlson comorbidity score</t>
-  </si>
-  <si>
-    <t>{:dps 0, :max 31, :min 2, :type :numeric}</t>
   </si>
   <si>
     <t>:smoking-history</t>
@@ -705,6 +699,12 @@
   </si>
   <si>
     <t>[:p "Age when the kidney cancer surgery was performed. Older patients are more at risk of other long-term health conditions and are relatively less likely to die from kidney cancer. An age between 25 and 85 may be entered here."]</t>
+  </si>
+  <si>
+    <t>{:dps 0, :max 31, :min 2, :type :numeric :validation "Score must be between 2 and 31"}</t>
+  </si>
+  <si>
+    <t>{:dps 0, :max 85, :min 25, :type :numeric :validation "Age must be between 25 and 85 years"}</t>
   </si>
 </sst>
 </file>
@@ -2314,13 +2314,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" t="s">
         <v>138</v>
-      </c>
-      <c r="B1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2342,7 +2342,7 @@
         <v>0.42</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4282,13 +4282,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" t="s">
         <v>138</v>
-      </c>
-      <c r="B1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6415,7 +6415,7 @@
     </row>
     <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>19</v>
@@ -9072,11 +9072,11 @@
       <c r="D25" s="9"/>
       <c r="E25" s="53"/>
       <c r="F25" s="9" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I25" s="25">
         <v>100</v>
@@ -9094,13 +9094,13 @@
         <v>34</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="E26" s="53">
         <v>0</v>
@@ -9116,7 +9116,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="44">
@@ -9128,11 +9128,11 @@
         <v>34</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E27" s="53">
         <v>0</v>
@@ -9148,7 +9148,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="44">
@@ -9171,40 +9171,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="50" t="s">
+      <c r="D1" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="E1" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="F1" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="G1" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="H1" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="I1" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="J1" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="K1" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="L1" s="50" t="s">
         <v>121</v>
-      </c>
-      <c r="L1" s="50" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -9212,7 +9212,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" s="51">
         <v>0</v>
@@ -9250,7 +9250,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3" s="51">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="51">
         <v>0</v>
@@ -9326,7 +9326,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="51">
         <v>0</v>
@@ -9364,7 +9364,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="51">
         <v>0</v>
@@ -9402,7 +9402,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="51">
         <v>0</v>
@@ -9440,7 +9440,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="51">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="51">
         <v>0</v>
@@ -9516,7 +9516,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10" s="51">
         <v>0</v>
@@ -9554,7 +9554,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="51">
         <v>0</v>
@@ -9592,7 +9592,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="51">
         <v>0</v>
@@ -9630,7 +9630,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="51">
         <v>0</v>
@@ -9668,7 +9668,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="51">
         <v>0</v>
@@ -9706,7 +9706,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C15" s="51">
         <v>0</v>
@@ -9744,7 +9744,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="51">
         <v>0</v>
@@ -9782,7 +9782,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="51">
         <v>0</v>
@@ -9820,7 +9820,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" s="51">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="51">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>44</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" s="51">
         <v>0</v>
@@ -9972,7 +9972,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C22" s="51">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" s="51">
         <v>0</v>
@@ -10048,7 +10048,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C24" s="51">
         <v>0</v>
@@ -10086,7 +10086,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C25" s="51">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
@@ -10162,7 +10162,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C27" s="51">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="51">
         <v>0</v>
@@ -10238,7 +10238,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C29" s="51">
         <v>0</v>
@@ -10276,7 +10276,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="51">
         <v>0</v>
@@ -10314,7 +10314,7 @@
         <v>54</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C31" s="51">
         <v>0</v>
@@ -10352,7 +10352,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32" s="51">
         <v>0</v>
@@ -10390,7 +10390,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" s="51">
         <v>0.01</v>
@@ -10428,7 +10428,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" s="51">
         <v>0.01</v>
@@ -10466,7 +10466,7 @@
         <v>58</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35" s="51">
         <v>0.01</v>
@@ -10504,7 +10504,7 @@
         <v>59</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C36" s="51">
         <v>0.01</v>
@@ -10542,7 +10542,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C37" s="51">
         <v>0.01</v>
@@ -10580,7 +10580,7 @@
         <v>61</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" s="51">
         <v>0.01</v>
@@ -10618,7 +10618,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C39" s="51">
         <v>0.01</v>
@@ -10656,7 +10656,7 @@
         <v>63</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C40" s="51">
         <v>0.01</v>
@@ -10694,7 +10694,7 @@
         <v>64</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C41" s="51">
         <v>0.01</v>
@@ -10732,7 +10732,7 @@
         <v>65</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C42" s="51">
         <v>0.01</v>
@@ -10770,7 +10770,7 @@
         <v>66</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C43" s="51">
         <v>0.01</v>
@@ -10808,7 +10808,7 @@
         <v>67</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C44" s="51">
         <v>0.01</v>
@@ -10846,7 +10846,7 @@
         <v>68</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C45" s="51">
         <v>0.02</v>
@@ -10884,7 +10884,7 @@
         <v>69</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C46" s="51">
         <v>0.02</v>
@@ -10922,7 +10922,7 @@
         <v>70</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" s="51">
         <v>0.02</v>
@@ -10960,7 +10960,7 @@
         <v>71</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C48" s="51">
         <v>0.02</v>
@@ -10998,7 +10998,7 @@
         <v>72</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49" s="51">
         <v>0.02</v>
@@ -11036,7 +11036,7 @@
         <v>73</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C50" s="51">
         <v>0.02</v>
@@ -11074,7 +11074,7 @@
         <v>74</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C51" s="51">
         <v>0.03</v>
@@ -11112,7 +11112,7 @@
         <v>75</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C52" s="51">
         <v>0.03</v>
@@ -11150,7 +11150,7 @@
         <v>76</v>
       </c>
       <c r="B53" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C53" s="51">
         <v>0.03</v>
@@ -11188,7 +11188,7 @@
         <v>77</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C54" s="51">
         <v>0.04</v>
@@ -11226,7 +11226,7 @@
         <v>78</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" s="51">
         <v>0.04</v>
@@ -11264,7 +11264,7 @@
         <v>79</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C56" s="51">
         <v>0.05</v>
@@ -11302,7 +11302,7 @@
         <v>80</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C57" s="51">
         <v>0.05</v>
@@ -11340,7 +11340,7 @@
         <v>81</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C58" s="51">
         <v>0.06</v>
@@ -11378,7 +11378,7 @@
         <v>82</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C59" s="51">
         <v>7.0000000000000007E-2</v>
@@ -11416,7 +11416,7 @@
         <v>83</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C60" s="51">
         <v>7.0000000000000007E-2</v>
@@ -11454,7 +11454,7 @@
         <v>84</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C61" s="51">
         <v>0.08</v>
@@ -11492,7 +11492,7 @@
         <v>85</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C62" s="51">
         <v>0.09</v>
@@ -11530,7 +11530,7 @@
         <v>25</v>
       </c>
       <c r="B63" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C63" s="51">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>26</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C64" s="51">
         <v>0</v>
@@ -11606,7 +11606,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C65" s="51">
         <v>0</v>
@@ -11644,7 +11644,7 @@
         <v>28</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C66" s="51">
         <v>0</v>
@@ -11682,7 +11682,7 @@
         <v>29</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C67" s="51">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>30</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68" s="51">
         <v>0</v>
@@ -11758,7 +11758,7 @@
         <v>31</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C69" s="51">
         <v>0</v>
@@ -11796,7 +11796,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C70" s="51">
         <v>0</v>
@@ -11834,7 +11834,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C71" s="51">
         <v>0</v>
@@ -11872,7 +11872,7 @@
         <v>34</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C72" s="51">
         <v>0</v>
@@ -11910,7 +11910,7 @@
         <v>35</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C73" s="51">
         <v>0</v>
@@ -11948,7 +11948,7 @@
         <v>36</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C74" s="51">
         <v>0</v>
@@ -11986,7 +11986,7 @@
         <v>37</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C75" s="51">
         <v>0</v>
@@ -12024,7 +12024,7 @@
         <v>38</v>
       </c>
       <c r="B76" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C76" s="51">
         <v>0</v>
@@ -12062,7 +12062,7 @@
         <v>39</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C77" s="51">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>40</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C78" s="51">
         <v>0</v>
@@ -12138,7 +12138,7 @@
         <v>41</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79" s="51">
         <v>0</v>
@@ -12176,7 +12176,7 @@
         <v>42</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C80" s="51">
         <v>0</v>
@@ -12214,7 +12214,7 @@
         <v>43</v>
       </c>
       <c r="B81" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C81" s="51">
         <v>0</v>
@@ -12252,7 +12252,7 @@
         <v>44</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82" s="51">
         <v>0</v>
@@ -12290,7 +12290,7 @@
         <v>45</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C83" s="51">
         <v>0</v>
@@ -12328,7 +12328,7 @@
         <v>46</v>
       </c>
       <c r="B84" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C84" s="51">
         <v>0</v>
@@ -12366,7 +12366,7 @@
         <v>47</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C85" s="51">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>48</v>
       </c>
       <c r="B86" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C86" s="51">
         <v>0</v>
@@ -12442,7 +12442,7 @@
         <v>49</v>
       </c>
       <c r="B87" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C87" s="51">
         <v>0</v>
@@ -12480,7 +12480,7 @@
         <v>50</v>
       </c>
       <c r="B88" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C88" s="51">
         <v>0</v>
@@ -12518,7 +12518,7 @@
         <v>51</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C89" s="51">
         <v>0</v>
@@ -12556,7 +12556,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C90" s="51">
         <v>0</v>
@@ -12594,7 +12594,7 @@
         <v>53</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C91" s="51">
         <v>0</v>
@@ -12632,7 +12632,7 @@
         <v>54</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="51">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         <v>55</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C93" s="51">
         <v>0</v>
@@ -12708,7 +12708,7 @@
         <v>56</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C94" s="51">
         <v>0</v>
@@ -12746,7 +12746,7 @@
         <v>57</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C95" s="51">
         <v>0</v>
@@ -12784,7 +12784,7 @@
         <v>58</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C96" s="51">
         <v>0</v>
@@ -12822,7 +12822,7 @@
         <v>59</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C97" s="51">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         <v>60</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C98" s="51">
         <v>0</v>
@@ -12898,7 +12898,7 @@
         <v>61</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99" s="51">
         <v>0.01</v>
@@ -12936,7 +12936,7 @@
         <v>62</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C100" s="51">
         <v>0.01</v>
@@ -12974,7 +12974,7 @@
         <v>63</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C101" s="51">
         <v>0.01</v>
@@ -13012,7 +13012,7 @@
         <v>64</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="51">
         <v>0.01</v>
@@ -13050,7 +13050,7 @@
         <v>65</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C103" s="51">
         <v>0.01</v>
@@ -13088,7 +13088,7 @@
         <v>66</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C104" s="51">
         <v>0.01</v>
@@ -13126,7 +13126,7 @@
         <v>67</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C105" s="51">
         <v>0.01</v>
@@ -13164,7 +13164,7 @@
         <v>68</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C106" s="51">
         <v>0.01</v>
@@ -13202,7 +13202,7 @@
         <v>69</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C107" s="51">
         <v>0.01</v>
@@ -13240,7 +13240,7 @@
         <v>70</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C108" s="51">
         <v>0.01</v>
@@ -13278,7 +13278,7 @@
         <v>71</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C109" s="51">
         <v>0.01</v>
@@ -13316,7 +13316,7 @@
         <v>72</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C110" s="51">
         <v>0.01</v>
@@ -13354,7 +13354,7 @@
         <v>73</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C111" s="51">
         <v>0.02</v>
@@ -13392,7 +13392,7 @@
         <v>74</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C112" s="51">
         <v>0.02</v>
@@ -13430,7 +13430,7 @@
         <v>75</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C113" s="51">
         <v>0.02</v>
@@ -13468,7 +13468,7 @@
         <v>76</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C114" s="51">
         <v>0.02</v>
@@ -13506,7 +13506,7 @@
         <v>77</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C115" s="51">
         <v>0.03</v>
@@ -13544,7 +13544,7 @@
         <v>78</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C116" s="51">
         <v>0.03</v>
@@ -13582,7 +13582,7 @@
         <v>79</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C117" s="51">
         <v>0.03</v>
@@ -13620,7 +13620,7 @@
         <v>80</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C118" s="51">
         <v>0.04</v>
@@ -13658,7 +13658,7 @@
         <v>81</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C119" s="51">
         <v>0.04</v>
@@ -13696,7 +13696,7 @@
         <v>82</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C120" s="51">
         <v>0.05</v>
@@ -13734,7 +13734,7 @@
         <v>83</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C121" s="51">
         <v>0.05</v>
@@ -13772,7 +13772,7 @@
         <v>84</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C122" s="51">
         <v>0.06</v>
@@ -13810,7 +13810,7 @@
         <v>85</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C123" s="51">
         <v>7.0000000000000007E-2</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="9" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="61" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" s="61"/>
       <c r="C9" s="62" t="s">
@@ -13962,7 +13962,7 @@
     </row>
     <row r="10" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A10" s="61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="61"/>
       <c r="C10" s="62" t="s">
@@ -14054,7 +14054,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E2" s="52">
         <v>0</v>
@@ -14066,7 +14066,7 @@
         <v>50</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I2" s="43">
         <v>50</v>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E3" s="53">
         <v>1.2430000000000001</v>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="53">
         <v>1.6479999999999999</v>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" s="53">
         <v>1.6479999999999999</v>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I11" s="25">
         <v>70</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="49" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I19" s="25">
         <v>90</v>
@@ -14623,11 +14623,11 @@
       <c r="D21" s="9"/>
       <c r="E21" s="53"/>
       <c r="F21" s="9" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I21" s="25">
         <v>100</v>
@@ -14645,13 +14645,13 @@
         <v>34</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="E22" s="53">
         <v>0</v>
@@ -14667,7 +14667,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="44">
@@ -14679,11 +14679,11 @@
         <v>34</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" s="53">
         <v>0</v>
@@ -14699,7 +14699,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="44">
@@ -14708,20 +14708,20 @@
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="53"/>
       <c r="F24" s="9" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="49" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I24" s="25">
         <v>120</v>
@@ -14736,16 +14736,16 @@
     </row>
     <row r="25" spans="1:14" ht="30">
       <c r="A25" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="25" t="s">
         <v>132</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>134</v>
       </c>
       <c r="E25" s="53">
         <v>0</v>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I25" s="25">
         <v>130</v>
@@ -14772,14 +14772,14 @@
     </row>
     <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E26" s="53">
         <v>1</v>
@@ -14804,14 +14804,14 @@
     </row>
     <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E27" s="53">
         <v>2</v>

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp2\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD51361-C56E-4901-AD12-A9B8DCCF674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14699D6F-B27B-4E84-AEE9-27FAE52DD042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -701,10 +701,10 @@
     <t>[:p "Age when the kidney cancer surgery was performed. Older patients are more at risk of other long-term health conditions and are relatively less likely to die from kidney cancer. An age between 25 and 85 may be entered here."]</t>
   </si>
   <si>
-    <t>{:dps 0, :max 31, :min 2, :type :numeric :validation "Score must be between 2 and 31"}</t>
-  </si>
-  <si>
     <t>{:dps 0, :max 85, :min 25, :type :numeric :validation "Age must be between 25 and 85 years"}</t>
+  </si>
+  <si>
+    <t>{:dps 0, :max 31, :min 2, :type :numeric :validation "Score must be between 2 and 31"  :calc-workflow :charlson}</t>
   </si>
 </sst>
 </file>
@@ -9072,7 +9072,7 @@
       <c r="D25" s="9"/>
       <c r="E25" s="53"/>
       <c r="F25" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
@@ -14623,7 +14623,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="53"/>
       <c r="F21" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="49" t="s">
@@ -14717,7 +14717,7 @@
       <c r="D24" s="9"/>
       <c r="E24" s="53"/>
       <c r="F24" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="49" t="s">

--- a/resources/kcp-models-master.xlsx
+++ b/resources/kcp-models-master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp2\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kcp\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14699D6F-B27B-4E84-AEE9-27FAE52DD042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56A9581-4766-4D3C-9198-22122D9BB762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15285" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -609,9 +609,6 @@
     <t>Former tobacco use</t>
   </si>
   <si>
-    <t xml:space="preserve">Never Used Tobacco </t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
@@ -706,6 +703,9 @@
   <si>
     <t>{:dps 0, :max 31, :min 2, :type :numeric :validation "Score must be between 2 and 31"  :calc-workflow :charlson}</t>
   </si>
+  <si>
+    <t>Never used tobacco</t>
+  </si>
 </sst>
 </file>
 
@@ -714,7 +714,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
@@ -785,6 +785,12 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -956,7 +962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1058,6 +1064,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2201,12 +2208,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="44" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.6328125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.6328125" style="1"/>
+    <col min="3" max="6" width="8.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -2314,13 +2321,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
         <v>136</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>137</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2342,7 +2349,7 @@
         <v>0.42</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4282,13 +4289,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
         <v>136</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>137</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6246,19 +6253,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.453125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.453125" style="1"/>
+    <col min="1" max="1" width="8.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.45" customHeight="1">
+    <row r="1" spans="1:6" ht="15.4" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
@@ -6278,7 +6285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+    <row r="2" spans="1:6" ht="17.45" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>12</v>
       </c>
@@ -6377,14 +6384,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.453125" style="1"/>
+    <col min="1" max="1" width="7.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="8.44140625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -6415,7 +6422,7 @@
     </row>
     <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>19</v>
@@ -6487,13 +6494,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E203"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="8.453125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.453125" style="1"/>
+    <col min="1" max="1" width="14.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="8.44140625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -8182,12 +8189,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.453125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.453125" style="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
+    <col min="3" max="6" width="8.44140625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -8306,21 +8313,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="81" style="1" customWidth="1"/>
-    <col min="8" max="8" width="116.36328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="1" customWidth="1"/>
-    <col min="10" max="12" width="14.1796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="40.36328125" style="1" customWidth="1"/>
-    <col min="14" max="15" width="8.453125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.453125" style="1"/>
+    <col min="8" max="8" width="116.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.21875" style="1" customWidth="1"/>
+    <col min="10" max="12" width="14.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="40.33203125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="8.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.100000000000001" customHeight="1">
@@ -8367,7 +8374,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="156.9" customHeight="1">
+    <row r="2" spans="1:14" ht="156.94999999999999" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>30</v>
       </c>
@@ -8993,7 +9000,7 @@
       <c r="M22" s="4"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="1:14" ht="45.45" customHeight="1">
+    <row r="23" spans="1:14" ht="45.4" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -9072,11 +9079,11 @@
       <c r="D25" s="9"/>
       <c r="E25" s="53"/>
       <c r="F25" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I25" s="25">
         <v>100</v>
@@ -9169,7 +9176,7 @@
   <dimension ref="A1:L123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" ht="15.75">
       <c r="A1" s="50" t="s">
         <v>111</v>
       </c>
@@ -13851,12 +13858,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD640821-0FB9-4D59-BBAC-F550C45F339E}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.453125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.453125" style="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
+    <col min="3" max="6" width="8.44140625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.100000000000001" customHeight="1">
@@ -13983,20 +13990,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261E92C2-54DD-4827-851F-385906BB591F}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="81" style="1" customWidth="1"/>
-    <col min="8" max="8" width="116.36328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="1" customWidth="1"/>
-    <col min="10" max="12" width="14.1796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="40.36328125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.453125" style="1"/>
+    <col min="8" max="8" width="116.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.21875" style="1" customWidth="1"/>
+    <col min="10" max="12" width="14.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="40.33203125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.100000000000001" customHeight="1">
@@ -14043,7 +14050,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="156.9" customHeight="1">
+    <row r="2" spans="1:14" ht="156.94999999999999" customHeight="1">
       <c r="A2" s="42" t="s">
         <v>30</v>
       </c>
@@ -14066,7 +14073,7 @@
         <v>50</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I2" s="43">
         <v>50</v>
@@ -14333,7 +14340,7 @@
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I11" s="25">
         <v>70</v>
@@ -14544,7 +14551,7 @@
       <c r="M18" s="4"/>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="1:14" ht="45.45" customHeight="1">
+    <row r="19" spans="1:14" ht="45.4" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>32</v>
       </c>
@@ -14565,7 +14572,7 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I19" s="25">
         <v>90</v>
@@ -14623,11 +14630,11 @@
       <c r="D21" s="9"/>
       <c r="E21" s="53"/>
       <c r="F21" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I21" s="25">
         <v>100</v>
@@ -14717,11 +14724,11 @@
       <c r="D24" s="9"/>
       <c r="E24" s="53"/>
       <c r="F24" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I24" s="25">
         <v>120</v>
@@ -14739,7 +14746,7 @@
         <v>130</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>131</v>
@@ -14775,7 +14782,7 @@
         <v>130</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="25" t="s">
@@ -14807,11 +14814,11 @@
         <v>130</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="25" t="s">
-        <v>135</v>
+      <c r="D27" s="63" t="s">
+        <v>150</v>
       </c>
       <c r="E27" s="53">
         <v>2</v>
